--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A3C61C-184C-41D2-975E-C967FED6F1B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372F96D2-81BB-4DAD-AE01-98441BB125B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1479" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="91">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -296,6 +296,9 @@
   <si>
     <t>Te instantaneo en Polvo y bebida energetica</t>
   </si>
+  <si>
+    <t xml:space="preserve">Frijol Mungo </t>
+  </si>
 </sst>
 </file>
 
@@ -395,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -425,19 +428,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -493,8 +499,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J367" totalsRowShown="0" totalsRowDxfId="10">
-  <autoFilter ref="A1:J367" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J369" totalsRowShown="0" totalsRowDxfId="10">
+  <autoFilter ref="A1:J369" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
     <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="8"/>
@@ -502,11 +508,11 @@
     <tableColumn id="7" xr3:uid="{C3650C10-5CB4-45A7-9736-6A80A51D6F83}" name="TIPO DE SERVICIO"/>
     <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="7" totalsRowDxfId="6"/>
     <tableColumn id="18" xr3:uid="{33E6F7D3-8F24-4F60-BCE9-4590974B7832}" name="CONTENIDO"/>
-    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="0" totalsRowDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" dataDxfId="2" totalsRowDxfId="3">
+    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" dataDxfId="0" totalsRowDxfId="3">
       <calculatedColumnFormula>G2/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="2" totalsRowDxfId="1"/>
     <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -830,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:K367"/>
+  <dimension ref="A1:K369"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -840,7 +846,7 @@
     <col min="5" max="5" width="31" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.625" customWidth="1"/>
     <col min="7" max="7" width="16.75" style="2" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.875" style="13" customWidth="1"/>
     <col min="9" max="9" width="32" style="2" customWidth="1"/>
     <col min="10" max="10" width="19.375" customWidth="1"/>
     <col min="11" max="11" width="21.375" customWidth="1"/>
@@ -868,7 +874,7 @@
       <c r="G1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="13" t="s">
         <v>87</v>
       </c>
       <c r="I1" s="2" t="s">
@@ -903,8 +909,8 @@
       <c r="G2" s="2">
         <v>378000</v>
       </c>
-      <c r="H2" s="2">
-        <f>G2/1000</f>
+      <c r="H2" s="13">
+        <f t="shared" ref="H2:H65" si="0">G2/1000</f>
         <v>378</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -939,8 +945,8 @@
       <c r="G3" s="2">
         <v>151200</v>
       </c>
-      <c r="H3" s="2">
-        <f>G3/1000</f>
+      <c r="H3" s="13">
+        <f t="shared" si="0"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -975,8 +981,8 @@
       <c r="G4" s="2">
         <v>252000</v>
       </c>
-      <c r="H4" s="2">
-        <f>G4/1000</f>
+      <c r="H4" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -1011,8 +1017,8 @@
       <c r="G5" s="2">
         <v>252000</v>
       </c>
-      <c r="H5" s="2">
-        <f>G5/1000</f>
+      <c r="H5" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -1047,8 +1053,8 @@
       <c r="G6" s="2">
         <v>201600</v>
       </c>
-      <c r="H6" s="2">
-        <f>G6/1000</f>
+      <c r="H6" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -1083,8 +1089,8 @@
       <c r="G7" s="2">
         <v>50400</v>
       </c>
-      <c r="H7" s="2">
-        <f>G7/1000</f>
+      <c r="H7" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -1119,8 +1125,8 @@
       <c r="G8" s="2">
         <v>352800</v>
       </c>
-      <c r="H8" s="2">
-        <f>G8/1000</f>
+      <c r="H8" s="13">
+        <f t="shared" si="0"/>
         <v>352.8</v>
       </c>
       <c r="I8" s="2" t="s">
@@ -1155,8 +1161,8 @@
       <c r="G9" s="2">
         <v>252000</v>
       </c>
-      <c r="H9" s="2">
-        <f>G9/1000</f>
+      <c r="H9" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -1191,8 +1197,8 @@
       <c r="G10" s="2">
         <v>126000</v>
       </c>
-      <c r="H10" s="2">
-        <f>G10/1000</f>
+      <c r="H10" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -1227,8 +1233,8 @@
       <c r="G11" s="2">
         <v>252000</v>
       </c>
-      <c r="H11" s="2">
-        <f>G11/1000</f>
+      <c r="H11" s="13">
+        <f t="shared" si="0"/>
         <v>252</v>
       </c>
       <c r="I11" s="2" t="s">
@@ -1263,8 +1269,8 @@
       <c r="G12" s="2">
         <v>201600</v>
       </c>
-      <c r="H12" s="2">
-        <f>G12/1000</f>
+      <c r="H12" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -1299,8 +1305,8 @@
       <c r="G13" s="2">
         <v>50400</v>
       </c>
-      <c r="H13" s="2">
-        <f>G13/1000</f>
+      <c r="H13" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -1335,8 +1341,8 @@
       <c r="G14" s="2">
         <v>25200</v>
       </c>
-      <c r="H14" s="2">
-        <f>G14/1000</f>
+      <c r="H14" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I14" s="2" t="s">
@@ -1371,8 +1377,8 @@
       <c r="G15" s="2">
         <v>126000</v>
       </c>
-      <c r="H15" s="2">
-        <f>G15/1000</f>
+      <c r="H15" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -1407,8 +1413,8 @@
       <c r="G16" s="2">
         <v>25200</v>
       </c>
-      <c r="H16" s="2">
-        <f>G16/1000</f>
+      <c r="H16" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I16" s="2" t="s">
@@ -1443,8 +1449,8 @@
       <c r="G17" s="2">
         <v>25200</v>
       </c>
-      <c r="H17" s="2">
-        <f>G17/1000</f>
+      <c r="H17" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I17" s="2" t="s">
@@ -1479,8 +1485,8 @@
       <c r="G18" s="2">
         <v>75600</v>
       </c>
-      <c r="H18" s="2">
-        <f>G18/1000</f>
+      <c r="H18" s="13">
+        <f t="shared" si="0"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I18" s="2" t="s">
@@ -1515,8 +1521,8 @@
       <c r="G19" s="2">
         <v>126000</v>
       </c>
-      <c r="H19" s="2">
-        <f>G19/1000</f>
+      <c r="H19" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
@@ -1551,8 +1557,8 @@
       <c r="G20" s="2">
         <v>25200</v>
       </c>
-      <c r="H20" s="2">
-        <f>G20/1000</f>
+      <c r="H20" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I20" s="2" t="s">
@@ -1587,8 +1593,8 @@
       <c r="G21" s="2">
         <v>302400</v>
       </c>
-      <c r="H21" s="2">
-        <f>G21/1000</f>
+      <c r="H21" s="13">
+        <f t="shared" si="0"/>
         <v>302.39999999999998</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -1623,8 +1629,8 @@
       <c r="G22" s="2">
         <v>201600</v>
       </c>
-      <c r="H22" s="2">
-        <f>G22/1000</f>
+      <c r="H22" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I22" s="2" t="s">
@@ -1659,8 +1665,8 @@
       <c r="G23" s="2">
         <v>126000</v>
       </c>
-      <c r="H23" s="2">
-        <f>G23/1000</f>
+      <c r="H23" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
@@ -1695,8 +1701,8 @@
       <c r="G24" s="2">
         <v>100800</v>
       </c>
-      <c r="H24" s="2">
-        <f>G24/1000</f>
+      <c r="H24" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I24" s="2" t="s">
@@ -1731,8 +1737,8 @@
       <c r="G25" s="2">
         <v>126000</v>
       </c>
-      <c r="H25" s="2">
-        <f>G25/1000</f>
+      <c r="H25" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
@@ -1767,8 +1773,8 @@
       <c r="G26" s="2">
         <v>100800</v>
       </c>
-      <c r="H26" s="2">
-        <f>G26/1000</f>
+      <c r="H26" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I26" s="2" t="s">
@@ -1803,8 +1809,8 @@
       <c r="G27" s="2">
         <v>100800</v>
       </c>
-      <c r="H27" s="2">
-        <f>G27/1000</f>
+      <c r="H27" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -1839,8 +1845,8 @@
       <c r="G28" s="2">
         <v>50400</v>
       </c>
-      <c r="H28" s="2">
-        <f>G28/1000</f>
+      <c r="H28" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I28" s="2" t="s">
@@ -1875,8 +1881,8 @@
       <c r="G29" s="2">
         <v>50400</v>
       </c>
-      <c r="H29" s="2">
-        <f>G29/1000</f>
+      <c r="H29" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I29" s="2" t="s">
@@ -1911,8 +1917,8 @@
       <c r="G30" s="2">
         <v>201600</v>
       </c>
-      <c r="H30" s="2">
-        <f>G30/1000</f>
+      <c r="H30" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -1947,8 +1953,8 @@
       <c r="G31" s="2">
         <v>126000</v>
       </c>
-      <c r="H31" s="2">
-        <f>G31/1000</f>
+      <c r="H31" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I31" s="2" t="s">
@@ -1983,8 +1989,8 @@
       <c r="G32" s="2">
         <v>50400</v>
       </c>
-      <c r="H32" s="2">
-        <f>G32/1000</f>
+      <c r="H32" s="13">
+        <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
       <c r="I32" s="2" t="s">
@@ -2019,8 +2025,8 @@
       <c r="G33" s="2">
         <v>75600</v>
       </c>
-      <c r="H33" s="2">
-        <f>G33/1000</f>
+      <c r="H33" s="13">
+        <f t="shared" si="0"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I33" s="2" t="s">
@@ -2055,8 +2061,8 @@
       <c r="G34" s="2">
         <v>126000</v>
       </c>
-      <c r="H34" s="2">
-        <f>G34/1000</f>
+      <c r="H34" s="13">
+        <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="I34" s="2" t="s">
@@ -2091,8 +2097,8 @@
       <c r="G35" s="2">
         <v>17370</v>
       </c>
-      <c r="H35" s="2">
-        <f>G35/1000</f>
+      <c r="H35" s="13">
+        <f t="shared" si="0"/>
         <v>17.37</v>
       </c>
       <c r="I35" s="2" t="s">
@@ -2127,8 +2133,8 @@
       <c r="G36" s="2">
         <v>45758</v>
       </c>
-      <c r="H36" s="2">
-        <f>G36/1000</f>
+      <c r="H36" s="13">
+        <f t="shared" si="0"/>
         <v>45.758000000000003</v>
       </c>
       <c r="I36" s="2" t="s">
@@ -2163,8 +2169,8 @@
       <c r="G37" s="2">
         <v>88100</v>
       </c>
-      <c r="H37" s="2">
-        <f>G37/1000</f>
+      <c r="H37" s="13">
+        <f t="shared" si="0"/>
         <v>88.1</v>
       </c>
       <c r="I37" s="2" t="s">
@@ -2199,8 +2205,8 @@
       <c r="G38" s="2">
         <v>70200</v>
       </c>
-      <c r="H38" s="2">
-        <f>G38/1000</f>
+      <c r="H38" s="13">
+        <f t="shared" si="0"/>
         <v>70.2</v>
       </c>
       <c r="I38" s="2" t="s">
@@ -2235,8 +2241,8 @@
       <c r="G39" s="2">
         <v>23480</v>
       </c>
-      <c r="H39" s="2">
-        <f>G39/1000</f>
+      <c r="H39" s="13">
+        <f t="shared" si="0"/>
         <v>23.48</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2271,8 +2277,8 @@
       <c r="G40" s="2">
         <v>119220</v>
       </c>
-      <c r="H40" s="2">
-        <f>G40/1000</f>
+      <c r="H40" s="13">
+        <f t="shared" si="0"/>
         <v>119.22</v>
       </c>
       <c r="I40" s="2" t="s">
@@ -2307,8 +2313,8 @@
       <c r="G41" s="2">
         <v>75250</v>
       </c>
-      <c r="H41" s="2">
-        <f>G41/1000</f>
+      <c r="H41" s="13">
+        <f t="shared" si="0"/>
         <v>75.25</v>
       </c>
       <c r="I41" s="2" t="s">
@@ -2343,8 +2349,8 @@
       <c r="G42" s="2">
         <v>70766</v>
       </c>
-      <c r="H42" s="2">
-        <f>G42/1000</f>
+      <c r="H42" s="13">
+        <f t="shared" si="0"/>
         <v>70.766000000000005</v>
       </c>
       <c r="I42" s="2" t="s">
@@ -2379,8 +2385,8 @@
       <c r="G43" s="2">
         <v>211998</v>
       </c>
-      <c r="H43" s="2">
-        <f>G43/1000</f>
+      <c r="H43" s="13">
+        <f t="shared" si="0"/>
         <v>211.99799999999999</v>
       </c>
       <c r="I43" s="2" t="s">
@@ -2415,8 +2421,8 @@
       <c r="G44" s="2">
         <v>141332</v>
       </c>
-      <c r="H44" s="2">
-        <f>G44/1000</f>
+      <c r="H44" s="13">
+        <f t="shared" si="0"/>
         <v>141.33199999999999</v>
       </c>
       <c r="I44" s="2" t="s">
@@ -2451,8 +2457,8 @@
       <c r="G45" s="2">
         <v>70666</v>
       </c>
-      <c r="H45" s="2">
-        <f>G45/1000</f>
+      <c r="H45" s="13">
+        <f t="shared" si="0"/>
         <v>70.665999999999997</v>
       </c>
       <c r="I45" s="2" t="s">
@@ -2487,8 +2493,8 @@
       <c r="G46" s="2">
         <v>71000</v>
       </c>
-      <c r="H46" s="2">
-        <f>G46/1000</f>
+      <c r="H46" s="13">
+        <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="I46" s="2" t="s">
@@ -2523,8 +2529,8 @@
       <c r="G47" s="2">
         <v>23940</v>
       </c>
-      <c r="H47" s="2">
-        <f>G47/1000</f>
+      <c r="H47" s="13">
+        <f t="shared" si="0"/>
         <v>23.94</v>
       </c>
       <c r="I47" s="2" t="s">
@@ -2559,8 +2565,8 @@
       <c r="G48" s="2">
         <v>30136.400000000001</v>
       </c>
-      <c r="H48" s="2">
-        <f>G48/1000</f>
+      <c r="H48" s="13">
+        <f t="shared" si="0"/>
         <v>30.136400000000002</v>
       </c>
       <c r="I48" s="2" t="s">
@@ -2595,8 +2601,8 @@
       <c r="G49" s="2">
         <v>100190.32</v>
       </c>
-      <c r="H49" s="2">
-        <f>G49/1000</f>
+      <c r="H49" s="13">
+        <f t="shared" si="0"/>
         <v>100.19032000000001</v>
       </c>
       <c r="I49" s="2" t="s">
@@ -2631,8 +2637,8 @@
       <c r="G50" s="2">
         <v>100880</v>
       </c>
-      <c r="H50" s="2">
-        <f>G50/1000</f>
+      <c r="H50" s="13">
+        <f t="shared" si="0"/>
         <v>100.88</v>
       </c>
       <c r="I50" s="2" t="s">
@@ -2667,8 +2673,8 @@
       <c r="G51" s="2">
         <v>100800</v>
       </c>
-      <c r="H51" s="2">
-        <f>G51/1000</f>
+      <c r="H51" s="13">
+        <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
       <c r="I51" s="2" t="s">
@@ -2703,8 +2709,8 @@
       <c r="G52" s="2">
         <v>201600</v>
       </c>
-      <c r="H52" s="2">
-        <f>G52/1000</f>
+      <c r="H52" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I52" s="2" t="s">
@@ -2739,8 +2745,8 @@
       <c r="G53" s="2">
         <v>25200</v>
       </c>
-      <c r="H53" s="2">
-        <f>G53/1000</f>
+      <c r="H53" s="13">
+        <f t="shared" si="0"/>
         <v>25.2</v>
       </c>
       <c r="I53" s="2" t="s">
@@ -2775,8 +2781,8 @@
       <c r="G54" s="2">
         <v>75300</v>
       </c>
-      <c r="H54" s="2">
-        <f>G54/1000</f>
+      <c r="H54" s="13">
+        <f t="shared" si="0"/>
         <v>75.3</v>
       </c>
       <c r="I54" s="2" t="s">
@@ -2811,8 +2817,8 @@
       <c r="G55" s="2">
         <v>151200</v>
       </c>
-      <c r="H55" s="2">
-        <f>G55/1000</f>
+      <c r="H55" s="13">
+        <f t="shared" si="0"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I55" s="2" t="s">
@@ -2847,8 +2853,8 @@
       <c r="G56" s="2">
         <v>25100</v>
       </c>
-      <c r="H56" s="2">
-        <f>G56/1000</f>
+      <c r="H56" s="13">
+        <f t="shared" si="0"/>
         <v>25.1</v>
       </c>
       <c r="I56" s="2" t="s">
@@ -2883,8 +2889,8 @@
       <c r="G57" s="2">
         <v>201600</v>
       </c>
-      <c r="H57" s="2">
-        <f>G57/1000</f>
+      <c r="H57" s="13">
+        <f t="shared" si="0"/>
         <v>201.6</v>
       </c>
       <c r="I57" s="2" t="s">
@@ -2919,8 +2925,8 @@
       <c r="G58" s="2">
         <v>28000</v>
       </c>
-      <c r="H58" s="2">
-        <f>G58/1000</f>
+      <c r="H58" s="13">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I58" s="2" t="s">
@@ -2955,8 +2961,8 @@
       <c r="G59" s="2">
         <v>28000</v>
       </c>
-      <c r="H59" s="2">
-        <f>G59/1000</f>
+      <c r="H59" s="13">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I59" s="2" t="s">
@@ -2991,8 +2997,8 @@
       <c r="G60" s="2">
         <v>28000</v>
       </c>
-      <c r="H60" s="2">
-        <f>G60/1000</f>
+      <c r="H60" s="13">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="I60" s="2" t="s">
@@ -3027,8 +3033,8 @@
       <c r="G61" s="2">
         <v>56280.000000000007</v>
       </c>
-      <c r="H61" s="2">
-        <f>G61/1000</f>
+      <c r="H61" s="13">
+        <f t="shared" si="0"/>
         <v>56.280000000000008</v>
       </c>
       <c r="I61" s="2" t="s">
@@ -3063,8 +3069,8 @@
       <c r="G62" s="2">
         <v>0</v>
       </c>
-      <c r="H62" s="2">
-        <f>G62/1000</f>
+      <c r="H62" s="13">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I62" t="s">
@@ -3099,8 +3105,8 @@
       <c r="G63" s="2">
         <v>25280</v>
       </c>
-      <c r="H63" s="2">
-        <f>G63/1000</f>
+      <c r="H63" s="13">
+        <f t="shared" si="0"/>
         <v>25.28</v>
       </c>
       <c r="I63" s="2" t="s">
@@ -3135,8 +3141,8 @@
       <c r="G64" s="2">
         <v>101220</v>
       </c>
-      <c r="H64" s="2">
-        <f>G64/1000</f>
+      <c r="H64" s="13">
+        <f t="shared" si="0"/>
         <v>101.22</v>
       </c>
       <c r="I64" s="2" t="s">
@@ -3171,8 +3177,8 @@
       <c r="G65" s="2">
         <v>25560</v>
       </c>
-      <c r="H65" s="2">
-        <f>G65/1000</f>
+      <c r="H65" s="13">
+        <f t="shared" si="0"/>
         <v>25.56</v>
       </c>
       <c r="I65" s="2" t="s">
@@ -3207,8 +3213,8 @@
       <c r="G66" s="2">
         <v>25360</v>
       </c>
-      <c r="H66" s="2">
-        <f>G66/1000</f>
+      <c r="H66" s="13">
+        <f t="shared" ref="H66:H129" si="1">G66/1000</f>
         <v>25.36</v>
       </c>
       <c r="I66" s="2" t="s">
@@ -3243,8 +3249,8 @@
       <c r="G67" s="2">
         <v>28880</v>
       </c>
-      <c r="H67" s="2">
-        <f>G67/1000</f>
+      <c r="H67" s="13">
+        <f t="shared" si="1"/>
         <v>28.88</v>
       </c>
       <c r="I67" s="2" t="s">
@@ -3279,8 +3285,8 @@
       <c r="G68" s="2">
         <v>50960</v>
       </c>
-      <c r="H68" s="2">
-        <f>G68/1000</f>
+      <c r="H68" s="13">
+        <f t="shared" si="1"/>
         <v>50.96</v>
       </c>
       <c r="I68" s="2" t="s">
@@ -3315,8 +3321,8 @@
       <c r="G69" s="2">
         <v>26820</v>
       </c>
-      <c r="H69" s="2">
-        <f>G69/1000</f>
+      <c r="H69" s="13">
+        <f t="shared" si="1"/>
         <v>26.82</v>
       </c>
       <c r="I69" s="2" t="s">
@@ -3351,8 +3357,8 @@
       <c r="G70" s="2">
         <v>0</v>
       </c>
-      <c r="H70" s="2">
-        <f>G70/1000</f>
+      <c r="H70" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I70" t="s">
@@ -3387,8 +3393,8 @@
       <c r="G71" s="2">
         <v>28000</v>
       </c>
-      <c r="H71" s="2">
-        <f>G71/1000</f>
+      <c r="H71" s="13">
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="I71" s="2" t="s">
@@ -3423,8 +3429,8 @@
       <c r="G72" s="2">
         <v>112560.00000000001</v>
       </c>
-      <c r="H72" s="2">
-        <f>G72/1000</f>
+      <c r="H72" s="13">
+        <f t="shared" si="1"/>
         <v>112.56000000000002</v>
       </c>
       <c r="I72" s="2" t="s">
@@ -3459,8 +3465,8 @@
       <c r="G73" s="2">
         <v>63100</v>
       </c>
-      <c r="H73" s="2">
-        <f>G73/1000</f>
+      <c r="H73" s="13">
+        <f t="shared" si="1"/>
         <v>63.1</v>
       </c>
       <c r="I73" s="2" t="s">
@@ -3495,8 +3501,8 @@
       <c r="G74" s="2">
         <v>253876</v>
       </c>
-      <c r="H74" s="2">
-        <f>G74/1000</f>
+      <c r="H74" s="13">
+        <f t="shared" si="1"/>
         <v>253.876</v>
       </c>
       <c r="I74" s="2" t="s">
@@ -3531,8 +3537,8 @@
       <c r="G75" s="2">
         <v>100860</v>
       </c>
-      <c r="H75" s="2">
-        <f>G75/1000</f>
+      <c r="H75" s="13">
+        <f t="shared" si="1"/>
         <v>100.86</v>
       </c>
       <c r="I75" s="2" t="s">
@@ -3567,8 +3573,8 @@
       <c r="G76" s="2">
         <v>25540</v>
       </c>
-      <c r="H76" s="2">
-        <f>G76/1000</f>
+      <c r="H76" s="13">
+        <f t="shared" si="1"/>
         <v>25.54</v>
       </c>
       <c r="I76" s="2" t="s">
@@ -3603,8 +3609,8 @@
       <c r="G77" s="2">
         <v>50500</v>
       </c>
-      <c r="H77" s="2">
-        <f>G77/1000</f>
+      <c r="H77" s="13">
+        <f t="shared" si="1"/>
         <v>50.5</v>
       </c>
       <c r="I77" s="2" t="s">
@@ -3639,8 +3645,8 @@
       <c r="G78" s="2">
         <v>50740</v>
       </c>
-      <c r="H78" s="2">
-        <f>G78/1000</f>
+      <c r="H78" s="13">
+        <f t="shared" si="1"/>
         <v>50.74</v>
       </c>
       <c r="I78" s="2" t="s">
@@ -3675,8 +3681,8 @@
       <c r="G79" s="2">
         <v>50580</v>
       </c>
-      <c r="H79" s="2">
-        <f>G79/1000</f>
+      <c r="H79" s="13">
+        <f t="shared" si="1"/>
         <v>50.58</v>
       </c>
       <c r="I79" s="2" t="s">
@@ -3711,8 +3717,8 @@
       <c r="G80" s="2">
         <v>151260</v>
       </c>
-      <c r="H80" s="2">
-        <f>G80/1000</f>
+      <c r="H80" s="13">
+        <f t="shared" si="1"/>
         <v>151.26</v>
       </c>
       <c r="I80" s="2" t="s">
@@ -3747,8 +3753,8 @@
       <c r="G81" s="2">
         <v>138530</v>
       </c>
-      <c r="H81" s="2">
-        <f>G81/1000</f>
+      <c r="H81" s="13">
+        <f t="shared" si="1"/>
         <v>138.53</v>
       </c>
       <c r="I81" s="2" t="s">
@@ -3783,8 +3789,8 @@
       <c r="G82" s="2">
         <v>253560</v>
       </c>
-      <c r="H82" s="2">
-        <f>G82/1000</f>
+      <c r="H82" s="13">
+        <f t="shared" si="1"/>
         <v>253.56</v>
       </c>
       <c r="I82" s="2" t="s">
@@ -3819,8 +3825,8 @@
       <c r="G83" s="2">
         <v>100860</v>
       </c>
-      <c r="H83" s="2">
-        <f>G83/1000</f>
+      <c r="H83" s="13">
+        <f t="shared" si="1"/>
         <v>100.86</v>
       </c>
       <c r="I83" s="2" t="s">
@@ -3855,8 +3861,8 @@
       <c r="G84" s="2">
         <v>379610</v>
       </c>
-      <c r="H84" s="2">
-        <f>G84/1000</f>
+      <c r="H84" s="13">
+        <f t="shared" si="1"/>
         <v>379.61</v>
       </c>
       <c r="I84" s="2" t="s">
@@ -3891,8 +3897,8 @@
       <c r="G85" s="2">
         <v>50420</v>
       </c>
-      <c r="H85" s="2">
-        <f>G85/1000</f>
+      <c r="H85" s="13">
+        <f t="shared" si="1"/>
         <v>50.42</v>
       </c>
       <c r="I85" s="2" t="s">
@@ -3927,8 +3933,8 @@
       <c r="G86" s="2">
         <v>252440</v>
       </c>
-      <c r="H86" s="2">
-        <f>G86/1000</f>
+      <c r="H86" s="13">
+        <f t="shared" si="1"/>
         <v>252.44</v>
       </c>
       <c r="I86" s="2" t="s">
@@ -3963,8 +3969,8 @@
       <c r="G87" s="2">
         <v>50400</v>
       </c>
-      <c r="H87" s="2">
-        <f>G87/1000</f>
+      <c r="H87" s="13">
+        <f t="shared" si="1"/>
         <v>50.4</v>
       </c>
       <c r="I87" s="2" t="s">
@@ -3999,8 +4005,8 @@
       <c r="G88" s="2">
         <v>0</v>
       </c>
-      <c r="H88" s="2">
-        <f>G88/1000</f>
+      <c r="H88" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I88" t="s">
@@ -4035,8 +4041,8 @@
       <c r="G89" s="2">
         <v>126760</v>
       </c>
-      <c r="H89" s="2">
-        <f>G89/1000</f>
+      <c r="H89" s="13">
+        <f t="shared" si="1"/>
         <v>126.76</v>
       </c>
       <c r="I89" s="2" t="s">
@@ -4071,8 +4077,8 @@
       <c r="G90" s="2">
         <v>227280</v>
       </c>
-      <c r="H90" s="2">
-        <f>G90/1000</f>
+      <c r="H90" s="13">
+        <f t="shared" si="1"/>
         <v>227.28</v>
       </c>
       <c r="I90" s="2" t="s">
@@ -4107,8 +4113,8 @@
       <c r="G91" s="2">
         <v>126160</v>
       </c>
-      <c r="H91" s="2">
-        <f>G91/1000</f>
+      <c r="H91" s="13">
+        <f t="shared" si="1"/>
         <v>126.16</v>
       </c>
       <c r="I91" s="2" t="s">
@@ -4143,8 +4149,8 @@
       <c r="G92" s="2">
         <v>126050</v>
       </c>
-      <c r="H92" s="2">
-        <f>G92/1000</f>
+      <c r="H92" s="13">
+        <f t="shared" si="1"/>
         <v>126.05</v>
       </c>
       <c r="I92" s="2" t="s">
@@ -4179,8 +4185,8 @@
       <c r="G93" s="2">
         <v>126360</v>
       </c>
-      <c r="H93" s="2">
-        <f>G93/1000</f>
+      <c r="H93" s="13">
+        <f t="shared" si="1"/>
         <v>126.36</v>
       </c>
       <c r="I93" s="2" t="s">
@@ -4215,8 +4221,8 @@
       <c r="G94" s="2">
         <v>25680</v>
       </c>
-      <c r="H94" s="2">
-        <f>G94/1000</f>
+      <c r="H94" s="13">
+        <f t="shared" si="1"/>
         <v>25.68</v>
       </c>
       <c r="I94" s="2" t="s">
@@ -4251,8 +4257,8 @@
       <c r="G95" s="2">
         <v>25380</v>
       </c>
-      <c r="H95" s="2">
-        <f>G95/1000</f>
+      <c r="H95" s="13">
+        <f t="shared" si="1"/>
         <v>25.38</v>
       </c>
       <c r="I95" s="2" t="s">
@@ -4287,8 +4293,8 @@
       <c r="G96" s="2">
         <v>25280</v>
       </c>
-      <c r="H96" s="2">
-        <f>G96/1000</f>
+      <c r="H96" s="13">
+        <f t="shared" si="1"/>
         <v>25.28</v>
       </c>
       <c r="I96" s="2" t="s">
@@ -4323,8 +4329,8 @@
       <c r="G97" s="2">
         <v>26660</v>
       </c>
-      <c r="H97" s="2">
-        <f>G97/1000</f>
+      <c r="H97" s="13">
+        <f t="shared" si="1"/>
         <v>26.66</v>
       </c>
       <c r="I97" s="2" t="s">
@@ -4359,8 +4365,8 @@
       <c r="G98" s="2">
         <v>157980</v>
       </c>
-      <c r="H98" s="2">
-        <f>G98/1000</f>
+      <c r="H98" s="13">
+        <f t="shared" si="1"/>
         <v>157.97999999999999</v>
       </c>
       <c r="I98" s="2" t="s">
@@ -4395,8 +4401,8 @@
       <c r="G99" s="2">
         <v>151740</v>
       </c>
-      <c r="H99" s="2">
-        <f>G99/1000</f>
+      <c r="H99" s="13">
+        <f t="shared" si="1"/>
         <v>151.74</v>
       </c>
       <c r="I99" s="2" t="s">
@@ -4431,8 +4437,8 @@
       <c r="G100" s="2">
         <v>75640</v>
       </c>
-      <c r="H100" s="2">
-        <f>G100/1000</f>
+      <c r="H100" s="13">
+        <f t="shared" si="1"/>
         <v>75.64</v>
       </c>
       <c r="I100" s="2" t="s">
@@ -4467,8 +4473,8 @@
       <c r="G101" s="2">
         <v>24200</v>
       </c>
-      <c r="H101" s="2">
-        <f>G101/1000</f>
+      <c r="H101" s="13">
+        <f t="shared" si="1"/>
         <v>24.2</v>
       </c>
       <c r="I101" s="2" t="s">
@@ -4503,8 +4509,8 @@
       <c r="G102" s="2">
         <v>0</v>
       </c>
-      <c r="H102" s="2">
-        <f>G102/1000</f>
+      <c r="H102" s="13">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I102" t="s">
@@ -4539,8 +4545,8 @@
       <c r="G103" s="2">
         <v>252080</v>
       </c>
-      <c r="H103" s="2">
-        <f>G103/1000</f>
+      <c r="H103" s="13">
+        <f t="shared" si="1"/>
         <v>252.08</v>
       </c>
       <c r="I103" s="2" t="s">
@@ -4575,8 +4581,8 @@
       <c r="G104" s="2">
         <v>100870</v>
       </c>
-      <c r="H104" s="2">
-        <f>G104/1000</f>
+      <c r="H104" s="13">
+        <f t="shared" si="1"/>
         <v>100.87</v>
       </c>
       <c r="I104" s="2" t="s">
@@ -4611,8 +4617,8 @@
       <c r="G105" s="2">
         <v>252980</v>
       </c>
-      <c r="H105" s="2">
-        <f>G105/1000</f>
+      <c r="H105" s="13">
+        <f t="shared" si="1"/>
         <v>252.98</v>
       </c>
       <c r="I105" s="2" t="s">
@@ -4647,8 +4653,8 @@
       <c r="G106" s="2">
         <v>126020</v>
       </c>
-      <c r="H106" s="2">
-        <f>G106/1000</f>
+      <c r="H106" s="13">
+        <f t="shared" si="1"/>
         <v>126.02</v>
       </c>
       <c r="I106" s="2" t="s">
@@ -4683,8 +4689,8 @@
       <c r="G107" s="2">
         <v>126580</v>
       </c>
-      <c r="H107" s="2">
-        <f>G107/1000</f>
+      <c r="H107" s="13">
+        <f t="shared" si="1"/>
         <v>126.58</v>
       </c>
       <c r="I107" s="2" t="s">
@@ -4719,8 +4725,8 @@
       <c r="G108" s="2">
         <v>21620</v>
       </c>
-      <c r="H108" s="2">
-        <f>G108/1000</f>
+      <c r="H108" s="13">
+        <f t="shared" si="1"/>
         <v>21.62</v>
       </c>
       <c r="I108" s="2" t="s">
@@ -4755,8 +4761,8 @@
       <c r="G109" s="2">
         <v>55310</v>
       </c>
-      <c r="H109" s="2">
-        <f>G109/1000</f>
+      <c r="H109" s="13">
+        <f t="shared" si="1"/>
         <v>55.31</v>
       </c>
       <c r="I109" s="2" t="s">
@@ -4791,8 +4797,8 @@
       <c r="G110" s="2">
         <v>100820</v>
       </c>
-      <c r="H110" s="2">
-        <f>G110/1000</f>
+      <c r="H110" s="13">
+        <f t="shared" si="1"/>
         <v>100.82</v>
       </c>
       <c r="I110" s="2" t="s">
@@ -4827,8 +4833,8 @@
       <c r="G111" s="2">
         <v>54560</v>
       </c>
-      <c r="H111" s="2">
-        <f>G111/1000</f>
+      <c r="H111" s="13">
+        <f t="shared" si="1"/>
         <v>54.56</v>
       </c>
       <c r="I111" s="2" t="s">
@@ -4863,8 +4869,8 @@
       <c r="G112" s="2">
         <v>21700</v>
       </c>
-      <c r="H112" s="2">
-        <f>G112/1000</f>
+      <c r="H112" s="13">
+        <f t="shared" si="1"/>
         <v>21.7</v>
       </c>
       <c r="I112" s="2" t="s">
@@ -4899,8 +4905,8 @@
       <c r="G113" s="2">
         <v>252290</v>
       </c>
-      <c r="H113" s="2">
-        <f>G113/1000</f>
+      <c r="H113" s="13">
+        <f t="shared" si="1"/>
         <v>252.29</v>
       </c>
       <c r="I113" s="2" t="s">
@@ -4935,8 +4941,8 @@
       <c r="G114" s="2">
         <v>252190</v>
       </c>
-      <c r="H114" s="2">
-        <f>G114/1000</f>
+      <c r="H114" s="13">
+        <f t="shared" si="1"/>
         <v>252.19</v>
       </c>
       <c r="I114" s="2" t="s">
@@ -4971,8 +4977,8 @@
       <c r="G115" s="2">
         <v>126360</v>
       </c>
-      <c r="H115" s="2">
-        <f>G115/1000</f>
+      <c r="H115" s="13">
+        <f t="shared" si="1"/>
         <v>126.36</v>
       </c>
       <c r="I115" s="2" t="s">
@@ -5007,8 +5013,8 @@
       <c r="G116" s="2">
         <v>100820</v>
       </c>
-      <c r="H116" s="2">
-        <f>G116/1000</f>
+      <c r="H116" s="13">
+        <f t="shared" si="1"/>
         <v>100.82</v>
       </c>
       <c r="I116" s="2" t="s">
@@ -5043,8 +5049,8 @@
       <c r="G117" s="2">
         <v>126240</v>
       </c>
-      <c r="H117" s="2">
-        <f>G117/1000</f>
+      <c r="H117" s="13">
+        <f t="shared" si="1"/>
         <v>126.24</v>
       </c>
       <c r="I117" s="2" t="s">
@@ -5079,8 +5085,8 @@
       <c r="G118" s="2">
         <v>126020</v>
       </c>
-      <c r="H118" s="2">
-        <f>G118/1000</f>
+      <c r="H118" s="13">
+        <f t="shared" si="1"/>
         <v>126.02</v>
       </c>
       <c r="I118" s="2" t="s">
@@ -5115,8 +5121,8 @@
       <c r="G119" s="2">
         <v>21700</v>
       </c>
-      <c r="H119" s="2">
-        <f>G119/1000</f>
+      <c r="H119" s="13">
+        <f t="shared" si="1"/>
         <v>21.7</v>
       </c>
       <c r="I119" s="2" t="s">
@@ -5151,8 +5157,8 @@
       <c r="G120" s="2">
         <v>151450</v>
       </c>
-      <c r="H120" s="2">
-        <f>G120/1000</f>
+      <c r="H120" s="13">
+        <f t="shared" si="1"/>
         <v>151.44999999999999</v>
       </c>
       <c r="I120" s="2" t="s">
@@ -5187,8 +5193,8 @@
       <c r="G121" s="2">
         <v>25200</v>
       </c>
-      <c r="H121" s="2">
-        <f>G121/1000</f>
+      <c r="H121" s="13">
+        <f t="shared" si="1"/>
         <v>25.2</v>
       </c>
       <c r="I121" s="2" t="s">
@@ -5223,8 +5229,8 @@
       <c r="G122" s="2">
         <v>126430</v>
       </c>
-      <c r="H122" s="2">
-        <f>G122/1000</f>
+      <c r="H122" s="13">
+        <f t="shared" si="1"/>
         <v>126.43</v>
       </c>
       <c r="I122" s="2" t="s">
@@ -5259,8 +5265,8 @@
       <c r="G123" s="2">
         <v>202110</v>
       </c>
-      <c r="H123" s="2">
-        <f>G123/1000</f>
+      <c r="H123" s="13">
+        <f t="shared" si="1"/>
         <v>202.11</v>
       </c>
       <c r="I123" s="2" t="s">
@@ -5295,8 +5301,8 @@
       <c r="G124" s="2">
         <v>126160</v>
       </c>
-      <c r="H124" s="2">
-        <f>G124/1000</f>
+      <c r="H124" s="13">
+        <f t="shared" si="1"/>
         <v>126.16</v>
       </c>
       <c r="I124" s="2" t="s">
@@ -5331,8 +5337,8 @@
       <c r="G125" s="2">
         <v>126090</v>
       </c>
-      <c r="H125" s="2">
-        <f>G125/1000</f>
+      <c r="H125" s="13">
+        <f t="shared" si="1"/>
         <v>126.09</v>
       </c>
       <c r="I125" s="2" t="s">
@@ -5367,8 +5373,8 @@
       <c r="G126" s="2">
         <v>119140</v>
       </c>
-      <c r="H126" s="2">
-        <f>G126/1000</f>
+      <c r="H126" s="13">
+        <f t="shared" si="1"/>
         <v>119.14</v>
       </c>
       <c r="I126" s="2" t="s">
@@ -5403,8 +5409,8 @@
       <c r="G127" s="2">
         <v>126070</v>
       </c>
-      <c r="H127" s="2">
-        <f>G127/1000</f>
+      <c r="H127" s="13">
+        <f t="shared" si="1"/>
         <v>126.07</v>
       </c>
       <c r="I127" s="2" t="s">
@@ -5439,8 +5445,8 @@
       <c r="G128" s="2">
         <v>76160</v>
       </c>
-      <c r="H128" s="2">
-        <f>G128/1000</f>
+      <c r="H128" s="13">
+        <f t="shared" si="1"/>
         <v>76.16</v>
       </c>
       <c r="I128" s="2" t="s">
@@ -5475,8 +5481,8 @@
       <c r="G129" s="2">
         <v>100950</v>
       </c>
-      <c r="H129" s="2">
-        <f>G129/1000</f>
+      <c r="H129" s="13">
+        <f t="shared" si="1"/>
         <v>100.95</v>
       </c>
       <c r="I129" s="2" t="s">
@@ -5511,8 +5517,8 @@
       <c r="G130" s="2">
         <v>126070</v>
       </c>
-      <c r="H130" s="2">
-        <f>G130/1000</f>
+      <c r="H130" s="13">
+        <f t="shared" ref="H130:H193" si="2">G130/1000</f>
         <v>126.07</v>
       </c>
       <c r="I130" s="2" t="s">
@@ -5547,8 +5553,8 @@
       <c r="G131" s="2">
         <v>126100</v>
       </c>
-      <c r="H131" s="2">
-        <f>G131/1000</f>
+      <c r="H131" s="13">
+        <f t="shared" si="2"/>
         <v>126.1</v>
       </c>
       <c r="I131" s="2" t="s">
@@ -5583,8 +5589,8 @@
       <c r="G132" s="2">
         <v>126000</v>
       </c>
-      <c r="H132" s="2">
-        <f>G132/1000</f>
+      <c r="H132" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I132" s="2" t="s">
@@ -5619,8 +5625,8 @@
       <c r="G133" s="2">
         <v>75600</v>
       </c>
-      <c r="H133" s="2">
-        <f>G133/1000</f>
+      <c r="H133" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I133" s="2" t="s">
@@ -5655,8 +5661,8 @@
       <c r="G134" s="2">
         <v>50400</v>
       </c>
-      <c r="H134" s="2">
-        <f>G134/1000</f>
+      <c r="H134" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I134" s="2" t="s">
@@ -5691,8 +5697,8 @@
       <c r="G135" s="2">
         <v>0</v>
       </c>
-      <c r="H135" s="2">
-        <f>G135/1000</f>
+      <c r="H135" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I135" t="s">
@@ -5727,8 +5733,8 @@
       <c r="G136" s="2">
         <v>0</v>
       </c>
-      <c r="H136" s="2">
-        <f>G136/1000</f>
+      <c r="H136" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I136" t="s">
@@ -5763,8 +5769,8 @@
       <c r="G137" s="2">
         <v>151200</v>
       </c>
-      <c r="H137" s="2">
-        <f>G137/1000</f>
+      <c r="H137" s="13">
+        <f t="shared" si="2"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I137" s="2" t="s">
@@ -5799,8 +5805,8 @@
       <c r="G138" s="2">
         <v>25200</v>
       </c>
-      <c r="H138" s="2">
-        <f>G138/1000</f>
+      <c r="H138" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I138" s="2" t="s">
@@ -5835,8 +5841,8 @@
       <c r="G139" s="2">
         <v>0</v>
       </c>
-      <c r="H139" s="2">
-        <f>G139/1000</f>
+      <c r="H139" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I139" t="s">
@@ -5871,8 +5877,8 @@
       <c r="G140" s="2">
         <v>100800</v>
       </c>
-      <c r="H140" s="2">
-        <f>G140/1000</f>
+      <c r="H140" s="13">
+        <f t="shared" si="2"/>
         <v>100.8</v>
       </c>
       <c r="I140" s="2" t="s">
@@ -5907,8 +5913,8 @@
       <c r="G141" s="2">
         <v>48788</v>
       </c>
-      <c r="H141" s="2">
-        <f>G141/1000</f>
+      <c r="H141" s="13">
+        <f t="shared" si="2"/>
         <v>48.787999999999997</v>
       </c>
       <c r="I141" s="2" t="s">
@@ -5943,8 +5949,8 @@
       <c r="G142" s="2">
         <v>126000</v>
       </c>
-      <c r="H142" s="2">
-        <f>G142/1000</f>
+      <c r="H142" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I142" s="2" t="s">
@@ -5979,8 +5985,8 @@
       <c r="G143" s="2">
         <v>25200</v>
       </c>
-      <c r="H143" s="2">
-        <f>G143/1000</f>
+      <c r="H143" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I143" s="2" t="s">
@@ -6015,8 +6021,8 @@
       <c r="G144" s="2">
         <v>7854</v>
       </c>
-      <c r="H144" s="2">
-        <f>G144/1000</f>
+      <c r="H144" s="13">
+        <f t="shared" si="2"/>
         <v>7.8540000000000001</v>
       </c>
       <c r="I144" s="2" t="s">
@@ -6051,8 +6057,8 @@
       <c r="G145" s="2">
         <v>252000</v>
       </c>
-      <c r="H145" s="2">
-        <f>G145/1000</f>
+      <c r="H145" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I145" s="2" t="s">
@@ -6087,8 +6093,8 @@
       <c r="G146" s="2">
         <v>50400</v>
       </c>
-      <c r="H146" s="2">
-        <f>G146/1000</f>
+      <c r="H146" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I146" s="2" t="s">
@@ -6123,8 +6129,8 @@
       <c r="G147" s="2">
         <v>50400</v>
       </c>
-      <c r="H147" s="2">
-        <f>G147/1000</f>
+      <c r="H147" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I147" s="2" t="s">
@@ -6159,8 +6165,8 @@
       <c r="G148" s="2">
         <v>126000</v>
       </c>
-      <c r="H148" s="2">
-        <f>G148/1000</f>
+      <c r="H148" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I148" s="2" t="s">
@@ -6195,8 +6201,8 @@
       <c r="G149" s="2">
         <v>75600</v>
       </c>
-      <c r="H149" s="2">
-        <f>G149/1000</f>
+      <c r="H149" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I149" s="2" t="s">
@@ -6231,8 +6237,8 @@
       <c r="G150" s="2">
         <v>50400</v>
       </c>
-      <c r="H150" s="2">
-        <f>G150/1000</f>
+      <c r="H150" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I150" s="2" t="s">
@@ -6267,8 +6273,8 @@
       <c r="G151" s="2">
         <v>252000</v>
       </c>
-      <c r="H151" s="2">
-        <f>G151/1000</f>
+      <c r="H151" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I151" s="2" t="s">
@@ -6303,8 +6309,8 @@
       <c r="G152" s="2">
         <v>252000</v>
       </c>
-      <c r="H152" s="2">
-        <f>G152/1000</f>
+      <c r="H152" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I152" s="2" t="s">
@@ -6339,8 +6345,8 @@
       <c r="G153" s="2">
         <v>50400</v>
       </c>
-      <c r="H153" s="2">
-        <f>G153/1000</f>
+      <c r="H153" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I153" s="2" t="s">
@@ -6375,8 +6381,8 @@
       <c r="G154" s="2">
         <v>126000</v>
       </c>
-      <c r="H154" s="2">
-        <f>G154/1000</f>
+      <c r="H154" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I154" s="2" t="s">
@@ -6411,8 +6417,8 @@
       <c r="G155" s="2">
         <v>252000</v>
       </c>
-      <c r="H155" s="2">
-        <f>G155/1000</f>
+      <c r="H155" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I155" s="2" t="s">
@@ -6447,8 +6453,8 @@
       <c r="G156" s="2">
         <v>252000</v>
       </c>
-      <c r="H156" s="2">
-        <f>G156/1000</f>
+      <c r="H156" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I156" s="2" t="s">
@@ -6483,8 +6489,8 @@
       <c r="G157" s="2">
         <v>25200</v>
       </c>
-      <c r="H157" s="2">
-        <f>G157/1000</f>
+      <c r="H157" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I157" s="2" t="s">
@@ -6519,8 +6525,8 @@
       <c r="G158" s="2">
         <v>75600</v>
       </c>
-      <c r="H158" s="2">
-        <f>G158/1000</f>
+      <c r="H158" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I158" s="2" t="s">
@@ -6555,8 +6561,8 @@
       <c r="G159" s="2">
         <v>50400</v>
       </c>
-      <c r="H159" s="2">
-        <f>G159/1000</f>
+      <c r="H159" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I159" s="2" t="s">
@@ -6591,8 +6597,8 @@
       <c r="G160" s="2">
         <v>0</v>
       </c>
-      <c r="H160" s="2">
-        <f>G160/1000</f>
+      <c r="H160" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I160" t="s">
@@ -6627,8 +6633,8 @@
       <c r="G161" s="2">
         <v>252000</v>
       </c>
-      <c r="H161" s="2">
-        <f>G161/1000</f>
+      <c r="H161" s="13">
+        <f t="shared" si="2"/>
         <v>252</v>
       </c>
       <c r="I161" s="2" t="s">
@@ -6663,8 +6669,8 @@
       <c r="G162" s="2">
         <v>0</v>
       </c>
-      <c r="H162" s="2">
-        <f>G162/1000</f>
+      <c r="H162" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I162" t="s">
@@ -6699,8 +6705,8 @@
       <c r="G163" s="2">
         <v>0</v>
       </c>
-      <c r="H163" s="2">
-        <f>G163/1000</f>
+      <c r="H163" s="13">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I163" t="s">
@@ -6735,8 +6741,8 @@
       <c r="G164" s="2">
         <v>50400</v>
       </c>
-      <c r="H164" s="2">
-        <f>G164/1000</f>
+      <c r="H164" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I164" s="2" t="s">
@@ -6771,8 +6777,8 @@
       <c r="G165" s="2">
         <v>50400</v>
       </c>
-      <c r="H165" s="2">
-        <f>G165/1000</f>
+      <c r="H165" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I165" s="2" t="s">
@@ -6807,8 +6813,8 @@
       <c r="G166" s="2">
         <v>151200</v>
       </c>
-      <c r="H166" s="2">
-        <f>G166/1000</f>
+      <c r="H166" s="13">
+        <f t="shared" si="2"/>
         <v>151.19999999999999</v>
       </c>
       <c r="I166" s="2" t="s">
@@ -6843,8 +6849,8 @@
       <c r="G167" s="2">
         <v>25960</v>
       </c>
-      <c r="H167" s="2">
-        <f>G167/1000</f>
+      <c r="H167" s="13">
+        <f t="shared" si="2"/>
         <v>25.96</v>
       </c>
       <c r="I167" s="2" t="s">
@@ -6879,8 +6885,8 @@
       <c r="G168" s="2">
         <v>8938</v>
       </c>
-      <c r="H168" s="2">
-        <f>G168/1000</f>
+      <c r="H168" s="13">
+        <f t="shared" si="2"/>
         <v>8.9380000000000006</v>
       </c>
       <c r="I168" s="2" t="s">
@@ -6915,8 +6921,8 @@
       <c r="G169" s="2">
         <v>100800</v>
       </c>
-      <c r="H169" s="2">
-        <f>G169/1000</f>
+      <c r="H169" s="13">
+        <f t="shared" si="2"/>
         <v>100.8</v>
       </c>
       <c r="I169" s="2" t="s">
@@ -6951,8 +6957,8 @@
       <c r="G170" s="2">
         <v>75600</v>
       </c>
-      <c r="H170" s="2">
-        <f>G170/1000</f>
+      <c r="H170" s="13">
+        <f t="shared" si="2"/>
         <v>75.599999999999994</v>
       </c>
       <c r="I170" s="2" t="s">
@@ -6987,8 +6993,8 @@
       <c r="G171" s="2">
         <v>62900</v>
       </c>
-      <c r="H171" s="2">
-        <f>G171/1000</f>
+      <c r="H171" s="13">
+        <f t="shared" si="2"/>
         <v>62.9</v>
       </c>
       <c r="I171" s="2" t="s">
@@ -7023,8 +7029,8 @@
       <c r="G172" s="2">
         <v>102290</v>
       </c>
-      <c r="H172" s="2">
-        <f>G172/1000</f>
+      <c r="H172" s="13">
+        <f t="shared" si="2"/>
         <v>102.29</v>
       </c>
       <c r="I172" s="2" t="s">
@@ -7059,8 +7065,8 @@
       <c r="G173" s="2">
         <v>189720</v>
       </c>
-      <c r="H173" s="2">
-        <f>G173/1000</f>
+      <c r="H173" s="13">
+        <f t="shared" si="2"/>
         <v>189.72</v>
       </c>
       <c r="I173" s="2" t="s">
@@ -7095,8 +7101,8 @@
       <c r="G174" s="2">
         <v>36870</v>
       </c>
-      <c r="H174" s="2">
-        <f>G174/1000</f>
+      <c r="H174" s="13">
+        <f t="shared" si="2"/>
         <v>36.869999999999997</v>
       </c>
       <c r="I174" s="2" t="s">
@@ -7131,8 +7137,8 @@
       <c r="G175" s="2">
         <v>40000</v>
       </c>
-      <c r="H175" s="2">
-        <f>G175/1000</f>
+      <c r="H175" s="13">
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="I175" s="2" t="s">
@@ -7167,8 +7173,8 @@
       <c r="G176" s="2">
         <v>25200</v>
       </c>
-      <c r="H176" s="2">
-        <f>G176/1000</f>
+      <c r="H176" s="13">
+        <f t="shared" si="2"/>
         <v>25.2</v>
       </c>
       <c r="I176" s="2" t="s">
@@ -7203,8 +7209,8 @@
       <c r="G177" s="2">
         <v>53900</v>
       </c>
-      <c r="H177" s="2">
-        <f>G177/1000</f>
+      <c r="H177" s="13">
+        <f t="shared" si="2"/>
         <v>53.9</v>
       </c>
       <c r="I177" s="2" t="s">
@@ -7239,8 +7245,8 @@
       <c r="G178" s="2">
         <v>28010</v>
       </c>
-      <c r="H178" s="2">
-        <f>G178/1000</f>
+      <c r="H178" s="13">
+        <f t="shared" si="2"/>
         <v>28.01</v>
       </c>
       <c r="I178" s="2" t="s">
@@ -7275,8 +7281,8 @@
       <c r="G179" s="2">
         <v>118248</v>
       </c>
-      <c r="H179" s="2">
-        <f>G179/1000</f>
+      <c r="H179" s="13">
+        <f t="shared" si="2"/>
         <v>118.248</v>
       </c>
       <c r="I179" s="2" t="s">
@@ -7311,8 +7317,8 @@
       <c r="G180" s="2">
         <v>5036</v>
       </c>
-      <c r="H180" s="2">
-        <f>G180/1000</f>
+      <c r="H180" s="13">
+        <f t="shared" si="2"/>
         <v>5.0359999999999996</v>
       </c>
       <c r="I180" s="2" t="s">
@@ -7347,8 +7353,8 @@
       <c r="G181" s="2">
         <v>28150</v>
       </c>
-      <c r="H181" s="2">
-        <f>G181/1000</f>
+      <c r="H181" s="13">
+        <f t="shared" si="2"/>
         <v>28.15</v>
       </c>
       <c r="I181" s="2" t="s">
@@ -7383,8 +7389,8 @@
       <c r="G182" s="2">
         <v>28150</v>
       </c>
-      <c r="H182" s="2">
-        <f>G182/1000</f>
+      <c r="H182" s="13">
+        <f t="shared" si="2"/>
         <v>28.15</v>
       </c>
       <c r="I182" s="2" t="s">
@@ -7419,8 +7425,8 @@
       <c r="G183" s="2">
         <v>60400</v>
       </c>
-      <c r="H183" s="2">
-        <f>G183/1000</f>
+      <c r="H183" s="13">
+        <f t="shared" si="2"/>
         <v>60.4</v>
       </c>
       <c r="I183" s="2" t="s">
@@ -7455,8 +7461,8 @@
       <c r="G184" s="2">
         <v>127173.11</v>
       </c>
-      <c r="H184" s="2">
-        <f>G184/1000</f>
+      <c r="H184" s="13">
+        <f t="shared" si="2"/>
         <v>127.17310999999999</v>
       </c>
       <c r="I184" s="2" t="s">
@@ -7491,8 +7497,8 @@
       <c r="G185" s="2">
         <v>80908</v>
       </c>
-      <c r="H185" s="2">
-        <f>G185/1000</f>
+      <c r="H185" s="13">
+        <f t="shared" si="2"/>
         <v>80.908000000000001</v>
       </c>
       <c r="I185" s="2" t="s">
@@ -7527,8 +7533,8 @@
       <c r="G186" s="2">
         <v>126000</v>
       </c>
-      <c r="H186" s="2">
-        <f>G186/1000</f>
+      <c r="H186" s="13">
+        <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="I186" s="2" t="s">
@@ -7563,8 +7569,8 @@
       <c r="G187" s="2">
         <v>101730</v>
       </c>
-      <c r="H187" s="2">
-        <f>G187/1000</f>
+      <c r="H187" s="13">
+        <f t="shared" si="2"/>
         <v>101.73</v>
       </c>
       <c r="I187" s="2" t="s">
@@ -7599,8 +7605,8 @@
       <c r="G188" s="2">
         <v>74919.81</v>
       </c>
-      <c r="H188" s="2">
-        <f>G188/1000</f>
+      <c r="H188" s="13">
+        <f t="shared" si="2"/>
         <v>74.919809999999998</v>
       </c>
       <c r="I188" s="2" t="s">
@@ -7635,8 +7641,8 @@
       <c r="G189" s="2">
         <v>175344.14</v>
       </c>
-      <c r="H189" s="2">
-        <f>G189/1000</f>
+      <c r="H189" s="13">
+        <f t="shared" si="2"/>
         <v>175.34414000000001</v>
       </c>
       <c r="I189" s="2" t="s">
@@ -7671,8 +7677,8 @@
       <c r="G190" s="2">
         <v>118629.95</v>
       </c>
-      <c r="H190" s="2">
-        <f>G190/1000</f>
+      <c r="H190" s="13">
+        <f t="shared" si="2"/>
         <v>118.62994999999999</v>
       </c>
       <c r="I190" s="2" t="s">
@@ -7707,8 +7713,8 @@
       <c r="G191" s="2">
         <v>50400</v>
       </c>
-      <c r="H191" s="2">
-        <f>G191/1000</f>
+      <c r="H191" s="13">
+        <f t="shared" si="2"/>
         <v>50.4</v>
       </c>
       <c r="I191" s="2" t="s">
@@ -7743,8 +7749,8 @@
       <c r="G192" s="2">
         <v>126080</v>
       </c>
-      <c r="H192" s="2">
-        <f>G192/1000</f>
+      <c r="H192" s="13">
+        <f t="shared" si="2"/>
         <v>126.08</v>
       </c>
       <c r="I192" s="2" t="s">
@@ -7779,8 +7785,8 @@
       <c r="G193" s="2">
         <v>50440</v>
       </c>
-      <c r="H193" s="2">
-        <f>G193/1000</f>
+      <c r="H193" s="13">
+        <f t="shared" si="2"/>
         <v>50.44</v>
       </c>
       <c r="I193" s="2" t="s">
@@ -7815,8 +7821,8 @@
       <c r="G194" s="2">
         <v>25220</v>
       </c>
-      <c r="H194" s="2">
-        <f>G194/1000</f>
+      <c r="H194" s="13">
+        <f t="shared" ref="H194:H257" si="3">G194/1000</f>
         <v>25.22</v>
       </c>
       <c r="I194" s="2" t="s">
@@ -7851,8 +7857,8 @@
       <c r="G195" s="2">
         <v>67566.14</v>
       </c>
-      <c r="H195" s="2">
-        <f>G195/1000</f>
+      <c r="H195" s="13">
+        <f t="shared" si="3"/>
         <v>67.566140000000004</v>
       </c>
       <c r="I195" s="2" t="s">
@@ -7887,8 +7893,8 @@
       <c r="G196" s="2">
         <v>50440</v>
       </c>
-      <c r="H196" s="2">
-        <f>G196/1000</f>
+      <c r="H196" s="13">
+        <f t="shared" si="3"/>
         <v>50.44</v>
       </c>
       <c r="I196" s="2" t="s">
@@ -7923,8 +7929,8 @@
       <c r="G197" s="2">
         <v>50200</v>
       </c>
-      <c r="H197" s="2">
-        <f>G197/1000</f>
+      <c r="H197" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I197" s="2" t="s">
@@ -7959,8 +7965,8 @@
       <c r="G198" s="2">
         <v>25690</v>
       </c>
-      <c r="H198" s="2">
-        <f>G198/1000</f>
+      <c r="H198" s="13">
+        <f t="shared" si="3"/>
         <v>25.69</v>
       </c>
       <c r="I198" s="2" t="s">
@@ -7995,8 +8001,8 @@
       <c r="G199" s="2">
         <v>25100</v>
       </c>
-      <c r="H199" s="2">
-        <f>G199/1000</f>
+      <c r="H199" s="13">
+        <f t="shared" si="3"/>
         <v>25.1</v>
       </c>
       <c r="I199" s="2" t="s">
@@ -8031,8 +8037,8 @@
       <c r="G200" s="2">
         <v>51208</v>
       </c>
-      <c r="H200" s="2">
-        <f>G200/1000</f>
+      <c r="H200" s="13">
+        <f t="shared" si="3"/>
         <v>51.207999999999998</v>
       </c>
       <c r="I200" s="2" t="s">
@@ -8067,8 +8073,8 @@
       <c r="G201" s="2">
         <v>70000</v>
       </c>
-      <c r="H201" s="2">
-        <f>G201/1000</f>
+      <c r="H201" s="13">
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="I201" s="2" t="s">
@@ -8103,8 +8109,8 @@
       <c r="G202" s="2">
         <v>39558</v>
       </c>
-      <c r="H202" s="2">
-        <f>G202/1000</f>
+      <c r="H202" s="13">
+        <f t="shared" si="3"/>
         <v>39.558</v>
       </c>
       <c r="I202" s="2" t="s">
@@ -8139,8 +8145,8 @@
       <c r="G203" s="2">
         <v>22000</v>
       </c>
-      <c r="H203" s="2">
-        <f>G203/1000</f>
+      <c r="H203" s="13">
+        <f t="shared" si="3"/>
         <v>22</v>
       </c>
       <c r="I203" s="2" t="s">
@@ -8175,8 +8181,8 @@
       <c r="G204" s="2">
         <v>100660</v>
       </c>
-      <c r="H204" s="2">
-        <f>G204/1000</f>
+      <c r="H204" s="13">
+        <f t="shared" si="3"/>
         <v>100.66</v>
       </c>
       <c r="I204" s="2" t="s">
@@ -8211,8 +8217,8 @@
       <c r="G205" s="2">
         <v>36600</v>
       </c>
-      <c r="H205" s="2">
-        <f>G205/1000</f>
+      <c r="H205" s="13">
+        <f t="shared" si="3"/>
         <v>36.6</v>
       </c>
       <c r="I205" s="2" t="s">
@@ -8247,8 +8253,8 @@
       <c r="G206" s="2">
         <v>50080</v>
       </c>
-      <c r="H206" s="2">
-        <f>G206/1000</f>
+      <c r="H206" s="13">
+        <f t="shared" si="3"/>
         <v>50.08</v>
       </c>
       <c r="I206" s="2" t="s">
@@ -8283,8 +8289,8 @@
       <c r="G207" s="2">
         <v>68160</v>
       </c>
-      <c r="H207" s="2">
-        <f>G207/1000</f>
+      <c r="H207" s="13">
+        <f t="shared" si="3"/>
         <v>68.16</v>
       </c>
       <c r="I207" s="2" t="s">
@@ -8319,8 +8325,8 @@
       <c r="G208" s="2">
         <v>43300</v>
       </c>
-      <c r="H208" s="2">
-        <f>G208/1000</f>
+      <c r="H208" s="13">
+        <f t="shared" si="3"/>
         <v>43.3</v>
       </c>
       <c r="I208" s="2" t="s">
@@ -8355,8 +8361,8 @@
       <c r="G209" s="2">
         <v>25060</v>
       </c>
-      <c r="H209" s="2">
-        <f>G209/1000</f>
+      <c r="H209" s="13">
+        <f t="shared" si="3"/>
         <v>25.06</v>
       </c>
       <c r="I209" s="2" t="s">
@@ -8391,8 +8397,8 @@
       <c r="G210" s="2">
         <v>125380</v>
       </c>
-      <c r="H210" s="2">
-        <f>G210/1000</f>
+      <c r="H210" s="13">
+        <f t="shared" si="3"/>
         <v>125.38</v>
       </c>
       <c r="I210" s="2" t="s">
@@ -8427,8 +8433,8 @@
       <c r="G211" s="2">
         <v>251000</v>
       </c>
-      <c r="H211" s="2">
-        <f>G211/1000</f>
+      <c r="H211" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I211" s="2" t="s">
@@ -8463,8 +8469,8 @@
       <c r="G212" s="2">
         <v>25080</v>
       </c>
-      <c r="H212" s="2">
-        <f>G212/1000</f>
+      <c r="H212" s="13">
+        <f t="shared" si="3"/>
         <v>25.08</v>
       </c>
       <c r="I212" s="2" t="s">
@@ -8499,8 +8505,8 @@
       <c r="G213" s="2">
         <v>22710</v>
       </c>
-      <c r="H213" s="2">
-        <f>G213/1000</f>
+      <c r="H213" s="13">
+        <f t="shared" si="3"/>
         <v>22.71</v>
       </c>
       <c r="I213" s="2" t="s">
@@ -8535,8 +8541,8 @@
       <c r="G214" s="2">
         <v>47340</v>
       </c>
-      <c r="H214" s="2">
-        <f>G214/1000</f>
+      <c r="H214" s="13">
+        <f t="shared" si="3"/>
         <v>47.34</v>
       </c>
       <c r="I214" s="2" t="s">
@@ -8571,8 +8577,8 @@
       <c r="G215" s="2">
         <v>125780</v>
       </c>
-      <c r="H215" s="2">
-        <f>G215/1000</f>
+      <c r="H215" s="13">
+        <f t="shared" si="3"/>
         <v>125.78</v>
       </c>
       <c r="I215" s="2" t="s">
@@ -8607,8 +8613,8 @@
       <c r="G216" s="2">
         <v>250960</v>
       </c>
-      <c r="H216" s="2">
-        <f>G216/1000</f>
+      <c r="H216" s="13">
+        <f t="shared" si="3"/>
         <v>250.96</v>
       </c>
       <c r="I216" s="2" t="s">
@@ -8643,8 +8649,8 @@
       <c r="G217" s="2">
         <v>250720</v>
       </c>
-      <c r="H217" s="2">
-        <f>G217/1000</f>
+      <c r="H217" s="13">
+        <f t="shared" si="3"/>
         <v>250.72</v>
       </c>
       <c r="I217" s="2" t="s">
@@ -8679,8 +8685,8 @@
       <c r="G218" s="2">
         <v>5374.8</v>
       </c>
-      <c r="H218" s="2">
-        <f>G218/1000</f>
+      <c r="H218" s="13">
+        <f t="shared" si="3"/>
         <v>5.3748000000000005</v>
       </c>
       <c r="I218" s="2" t="s">
@@ -8715,8 +8721,8 @@
       <c r="G219" s="2">
         <v>72160</v>
       </c>
-      <c r="H219" s="2">
-        <f>G219/1000</f>
+      <c r="H219" s="13">
+        <f t="shared" si="3"/>
         <v>72.16</v>
       </c>
       <c r="I219" s="2" t="s">
@@ -8751,8 +8757,8 @@
       <c r="G220" s="2">
         <v>50200</v>
       </c>
-      <c r="H220" s="2">
-        <f>G220/1000</f>
+      <c r="H220" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I220" s="2" t="s">
@@ -8787,8 +8793,8 @@
       <c r="G221" s="2">
         <v>40480</v>
       </c>
-      <c r="H221" s="2">
-        <f>G221/1000</f>
+      <c r="H221" s="13">
+        <f t="shared" si="3"/>
         <v>40.479999999999997</v>
       </c>
       <c r="I221" s="2" t="s">
@@ -8823,8 +8829,8 @@
       <c r="G222" s="2">
         <v>50040</v>
       </c>
-      <c r="H222" s="2">
-        <f>G222/1000</f>
+      <c r="H222" s="13">
+        <f t="shared" si="3"/>
         <v>50.04</v>
       </c>
       <c r="I222" s="2" t="s">
@@ -8859,8 +8865,8 @@
       <c r="G223" s="2">
         <v>50200</v>
       </c>
-      <c r="H223" s="2">
-        <f>G223/1000</f>
+      <c r="H223" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I223" s="2" t="s">
@@ -8895,8 +8901,8 @@
       <c r="G224" s="2">
         <v>45440</v>
       </c>
-      <c r="H224" s="2">
-        <f>G224/1000</f>
+      <c r="H224" s="13">
+        <f t="shared" si="3"/>
         <v>45.44</v>
       </c>
       <c r="I224" s="2" t="s">
@@ -8931,8 +8937,8 @@
       <c r="G225" s="2">
         <v>40000</v>
       </c>
-      <c r="H225" s="2">
-        <f>G225/1000</f>
+      <c r="H225" s="13">
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="I225" s="2" t="s">
@@ -8967,8 +8973,8 @@
       <c r="G226" s="2">
         <v>75000</v>
       </c>
-      <c r="H226" s="2">
-        <f>G226/1000</f>
+      <c r="H226" s="13">
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="I226" s="2" t="s">
@@ -9003,8 +9009,8 @@
       <c r="G227" s="2">
         <v>50000</v>
       </c>
-      <c r="H227" s="2">
-        <f>G227/1000</f>
+      <c r="H227" s="13">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
       <c r="I227" s="2" t="s">
@@ -9039,8 +9045,8 @@
       <c r="G228" s="2">
         <v>23250</v>
       </c>
-      <c r="H228" s="2">
-        <f>G228/1000</f>
+      <c r="H228" s="13">
+        <f t="shared" si="3"/>
         <v>23.25</v>
       </c>
       <c r="I228" s="2" t="s">
@@ -9075,8 +9081,8 @@
       <c r="G229" s="2">
         <v>75000</v>
       </c>
-      <c r="H229" s="2">
-        <f>G229/1000</f>
+      <c r="H229" s="13">
+        <f t="shared" si="3"/>
         <v>75</v>
       </c>
       <c r="I229" s="2" t="s">
@@ -9111,8 +9117,8 @@
       <c r="G230" s="2">
         <v>50200</v>
       </c>
-      <c r="H230" s="2">
-        <f>G230/1000</f>
+      <c r="H230" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I230" s="2" t="s">
@@ -9147,8 +9153,8 @@
       <c r="G231" s="2">
         <v>251000</v>
       </c>
-      <c r="H231" s="2">
-        <f>G231/1000</f>
+      <c r="H231" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I231" s="2" t="s">
@@ -9183,8 +9189,8 @@
       <c r="G232" s="2">
         <v>75300</v>
       </c>
-      <c r="H232" s="2">
-        <f>G232/1000</f>
+      <c r="H232" s="13">
+        <f t="shared" si="3"/>
         <v>75.3</v>
       </c>
       <c r="I232" s="2" t="s">
@@ -9219,8 +9225,8 @@
       <c r="G233" s="2">
         <v>125500</v>
       </c>
-      <c r="H233" s="2">
-        <f>G233/1000</f>
+      <c r="H233" s="13">
+        <f t="shared" si="3"/>
         <v>125.5</v>
       </c>
       <c r="I233" s="2" t="s">
@@ -9255,8 +9261,8 @@
       <c r="G234" s="2">
         <v>251000</v>
       </c>
-      <c r="H234" s="2">
-        <f>G234/1000</f>
+      <c r="H234" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I234" s="2" t="s">
@@ -9291,8 +9297,8 @@
       <c r="G235" s="2">
         <v>251000</v>
       </c>
-      <c r="H235" s="2">
-        <f>G235/1000</f>
+      <c r="H235" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I235" s="2" t="s">
@@ -9327,8 +9333,8 @@
       <c r="G236" s="2">
         <v>251000</v>
       </c>
-      <c r="H236" s="2">
-        <f>G236/1000</f>
+      <c r="H236" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I236" s="2" t="s">
@@ -9363,8 +9369,8 @@
       <c r="G237" s="2">
         <v>23680</v>
       </c>
-      <c r="H237" s="2">
-        <f>G237/1000</f>
+      <c r="H237" s="13">
+        <f t="shared" si="3"/>
         <v>23.68</v>
       </c>
       <c r="I237" s="2" t="s">
@@ -9399,8 +9405,8 @@
       <c r="G238" s="2">
         <v>1500</v>
       </c>
-      <c r="H238" s="2">
-        <f>G238/1000</f>
+      <c r="H238" s="13">
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="I238" s="2" t="s">
@@ -9435,8 +9441,8 @@
       <c r="G239" s="2">
         <v>50200</v>
       </c>
-      <c r="H239" s="2">
-        <f>G239/1000</f>
+      <c r="H239" s="13">
+        <f t="shared" si="3"/>
         <v>50.2</v>
       </c>
       <c r="I239" s="2" t="s">
@@ -9471,8 +9477,8 @@
       <c r="G240" s="2">
         <v>200800</v>
       </c>
-      <c r="H240" s="2">
-        <f>G240/1000</f>
+      <c r="H240" s="13">
+        <f t="shared" si="3"/>
         <v>200.8</v>
       </c>
       <c r="I240" s="2" t="s">
@@ -9507,8 +9513,8 @@
       <c r="G241" s="2">
         <v>100400</v>
       </c>
-      <c r="H241" s="2">
-        <f>G241/1000</f>
+      <c r="H241" s="13">
+        <f t="shared" si="3"/>
         <v>100.4</v>
       </c>
       <c r="I241" s="2" t="s">
@@ -9543,8 +9549,8 @@
       <c r="G242" s="2">
         <v>75300</v>
       </c>
-      <c r="H242" s="2">
-        <f>G242/1000</f>
+      <c r="H242" s="13">
+        <f t="shared" si="3"/>
         <v>75.3</v>
       </c>
       <c r="I242" s="2" t="s">
@@ -9579,8 +9585,8 @@
       <c r="G243" s="2">
         <v>25840</v>
       </c>
-      <c r="H243" s="2">
-        <f>G243/1000</f>
+      <c r="H243" s="13">
+        <f t="shared" si="3"/>
         <v>25.84</v>
       </c>
       <c r="I243" s="2" t="s">
@@ -9615,8 +9621,8 @@
       <c r="G244" s="2">
         <v>251000</v>
       </c>
-      <c r="H244" s="2">
-        <f>G244/1000</f>
+      <c r="H244" s="13">
+        <f t="shared" si="3"/>
         <v>251</v>
       </c>
       <c r="I244" s="2" t="s">
@@ -9651,8 +9657,8 @@
       <c r="G245" s="2">
         <v>150600</v>
       </c>
-      <c r="H245" s="2">
-        <f>G245/1000</f>
+      <c r="H245" s="13">
+        <f t="shared" si="3"/>
         <v>150.6</v>
       </c>
       <c r="I245" s="2" t="s">
@@ -9687,8 +9693,8 @@
       <c r="G246" s="2">
         <v>50040</v>
       </c>
-      <c r="H246" s="2">
-        <f>G246/1000</f>
+      <c r="H246" s="13">
+        <f t="shared" si="3"/>
         <v>50.04</v>
       </c>
       <c r="I246" s="2" t="s">
@@ -9723,8 +9729,8 @@
       <c r="G247" s="2">
         <v>9529</v>
       </c>
-      <c r="H247" s="2">
-        <f>G247/1000</f>
+      <c r="H247" s="13">
+        <f t="shared" si="3"/>
         <v>9.5289999999999999</v>
       </c>
       <c r="I247" s="2" t="s">
@@ -9759,8 +9765,8 @@
       <c r="G248" s="2">
         <v>367500</v>
       </c>
-      <c r="H248" s="2">
-        <f>G248/1000</f>
+      <c r="H248" s="13">
+        <f t="shared" si="3"/>
         <v>367.5</v>
       </c>
       <c r="I248" s="2" t="s">
@@ -9795,8 +9801,8 @@
       <c r="G249" s="2">
         <v>0</v>
       </c>
-      <c r="H249" s="2">
-        <f>G249/1000</f>
+      <c r="H249" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I249" t="s">
@@ -9831,8 +9837,8 @@
       <c r="G250" s="2">
         <v>0</v>
       </c>
-      <c r="H250" s="2">
-        <f>G250/1000</f>
+      <c r="H250" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I250" s="2" t="s">
@@ -9867,8 +9873,8 @@
       <c r="G251" s="2">
         <v>0</v>
       </c>
-      <c r="H251" s="2">
-        <f>G251/1000</f>
+      <c r="H251" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I251" s="2" t="s">
@@ -9903,8 +9909,8 @@
       <c r="G252" s="2">
         <v>0</v>
       </c>
-      <c r="H252" s="2">
-        <f>G252/1000</f>
+      <c r="H252" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I252" s="2" t="s">
@@ -9939,8 +9945,8 @@
       <c r="G253" s="2">
         <v>0</v>
       </c>
-      <c r="H253" s="2">
-        <f>G253/1000</f>
+      <c r="H253" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I253" s="2" t="s">
@@ -9975,8 +9981,8 @@
       <c r="G254" s="2">
         <v>0</v>
       </c>
-      <c r="H254" s="2">
-        <f>G254/1000</f>
+      <c r="H254" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I254" s="2" t="s">
@@ -10011,8 +10017,8 @@
       <c r="G255" s="2">
         <v>0</v>
       </c>
-      <c r="H255" s="2">
-        <f>G255/1000</f>
+      <c r="H255" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I255" s="2" t="s">
@@ -10047,8 +10053,8 @@
       <c r="G256" s="2">
         <v>0</v>
       </c>
-      <c r="H256" s="2">
-        <f>G256/1000</f>
+      <c r="H256" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I256" s="2" t="s">
@@ -10083,8 +10089,8 @@
       <c r="G257" s="2">
         <v>0</v>
       </c>
-      <c r="H257" s="2">
-        <f>G257/1000</f>
+      <c r="H257" s="13">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I257" s="2" t="s">
@@ -10119,8 +10125,8 @@
       <c r="G258" s="2">
         <v>0</v>
       </c>
-      <c r="H258" s="2">
-        <f>G258/1000</f>
+      <c r="H258" s="13">
+        <f t="shared" ref="H258:H321" si="4">G258/1000</f>
         <v>0</v>
       </c>
       <c r="I258" s="2" t="s">
@@ -10155,8 +10161,8 @@
       <c r="G259" s="2">
         <v>0</v>
       </c>
-      <c r="H259" s="2">
-        <f>G259/1000</f>
+      <c r="H259" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I259" t="s">
@@ -10191,8 +10197,8 @@
       <c r="G260" s="2">
         <v>0</v>
       </c>
-      <c r="H260" s="2">
-        <f>G260/1000</f>
+      <c r="H260" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I260" t="s">
@@ -10227,8 +10233,8 @@
       <c r="G261" s="2">
         <v>0</v>
       </c>
-      <c r="H261" s="2">
-        <f>G261/1000</f>
+      <c r="H261" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I261" t="s">
@@ -10263,8 +10269,8 @@
       <c r="G262" s="2">
         <v>140000</v>
       </c>
-      <c r="H262" s="2">
-        <f>G262/1000</f>
+      <c r="H262" s="13">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I262" s="2" t="s">
@@ -10299,8 +10305,8 @@
       <c r="G263" s="2">
         <v>0</v>
       </c>
-      <c r="H263" s="2">
-        <f>G263/1000</f>
+      <c r="H263" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I263" t="s">
@@ -10335,8 +10341,8 @@
       <c r="G264" s="2">
         <v>44760</v>
       </c>
-      <c r="H264" s="2">
-        <f>G264/1000</f>
+      <c r="H264" s="13">
+        <f t="shared" si="4"/>
         <v>44.76</v>
       </c>
       <c r="I264" s="2" t="s">
@@ -10371,8 +10377,8 @@
       <c r="G265" s="2">
         <v>25140</v>
       </c>
-      <c r="H265" s="2">
-        <f>G265/1000</f>
+      <c r="H265" s="13">
+        <f t="shared" si="4"/>
         <v>25.14</v>
       </c>
       <c r="I265" s="2" t="s">
@@ -10407,8 +10413,8 @@
       <c r="G266" s="2">
         <v>44360</v>
       </c>
-      <c r="H266" s="2">
-        <f>G266/1000</f>
+      <c r="H266" s="13">
+        <f t="shared" si="4"/>
         <v>44.36</v>
       </c>
       <c r="I266" s="2" t="s">
@@ -10443,8 +10449,8 @@
       <c r="G267" s="2">
         <v>70000</v>
       </c>
-      <c r="H267" s="2">
-        <f>G267/1000</f>
+      <c r="H267" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I267" s="2" t="s">
@@ -10479,8 +10485,8 @@
       <c r="G268" s="2">
         <v>25140</v>
       </c>
-      <c r="H268" s="2">
-        <f>G268/1000</f>
+      <c r="H268" s="13">
+        <f t="shared" si="4"/>
         <v>25.14</v>
       </c>
       <c r="I268" s="2" t="s">
@@ -10515,8 +10521,8 @@
       <c r="G269" s="2">
         <v>75000</v>
       </c>
-      <c r="H269" s="2">
-        <f>G269/1000</f>
+      <c r="H269" s="13">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="I269" s="2" t="s">
@@ -10551,8 +10557,8 @@
       <c r="G270" s="2">
         <v>25000</v>
       </c>
-      <c r="H270" s="2">
-        <f>G270/1000</f>
+      <c r="H270" s="13">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I270" s="2" t="s">
@@ -10587,8 +10593,8 @@
       <c r="G271" s="2">
         <v>125000</v>
       </c>
-      <c r="H271" s="2">
-        <f>G271/1000</f>
+      <c r="H271" s="13">
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="I271" s="2" t="s">
@@ -10623,8 +10629,8 @@
       <c r="G272" s="2">
         <v>43000</v>
       </c>
-      <c r="H272" s="2">
-        <f>G272/1000</f>
+      <c r="H272" s="13">
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="I272" s="2" t="s">
@@ -10659,8 +10665,8 @@
       <c r="G273" s="2">
         <v>70000</v>
       </c>
-      <c r="H273" s="2">
-        <f>G273/1000</f>
+      <c r="H273" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I273" s="2" t="s">
@@ -10695,8 +10701,8 @@
       <c r="G274" s="2">
         <v>125000</v>
       </c>
-      <c r="H274" s="2">
-        <f>G274/1000</f>
+      <c r="H274" s="13">
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="I274" s="2" t="s">
@@ -10731,8 +10737,8 @@
       <c r="G275" s="2">
         <v>70000</v>
       </c>
-      <c r="H275" s="2">
-        <f>G275/1000</f>
+      <c r="H275" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I275" s="2" t="s">
@@ -10767,8 +10773,8 @@
       <c r="G276" s="2">
         <v>250000</v>
       </c>
-      <c r="H276" s="2">
-        <f>G276/1000</f>
+      <c r="H276" s="13">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="I276" s="2" t="s">
@@ -10803,8 +10809,8 @@
       <c r="G277" s="2">
         <v>9000</v>
       </c>
-      <c r="H277" s="2">
-        <f>G277/1000</f>
+      <c r="H277" s="13">
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="I277" s="2" t="s">
@@ -10839,8 +10845,8 @@
       <c r="G278" s="2">
         <v>19200</v>
       </c>
-      <c r="H278" s="2">
-        <f>G278/1000</f>
+      <c r="H278" s="13">
+        <f t="shared" si="4"/>
         <v>19.2</v>
       </c>
       <c r="I278" s="2" t="s">
@@ -10875,8 +10881,8 @@
       <c r="G279" s="2">
         <v>250000</v>
       </c>
-      <c r="H279" s="2">
-        <f>G279/1000</f>
+      <c r="H279" s="13">
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="I279" s="2" t="s">
@@ -10911,8 +10917,8 @@
       <c r="G280" s="2">
         <v>140000</v>
       </c>
-      <c r="H280" s="2">
-        <f>G280/1000</f>
+      <c r="H280" s="13">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I280" s="2" t="s">
@@ -10947,8 +10953,8 @@
       <c r="G281" s="2">
         <v>125000</v>
       </c>
-      <c r="H281" s="2">
-        <f>G281/1000</f>
+      <c r="H281" s="13">
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="I281" s="2" t="s">
@@ -10983,8 +10989,8 @@
       <c r="G282" s="2">
         <v>19250</v>
       </c>
-      <c r="H282" s="2">
-        <f>G282/1000</f>
+      <c r="H282" s="13">
+        <f t="shared" si="4"/>
         <v>19.25</v>
       </c>
       <c r="I282" s="2" t="s">
@@ -11019,8 +11025,8 @@
       <c r="G283" s="2">
         <v>25000</v>
       </c>
-      <c r="H283" s="2">
-        <f>G283/1000</f>
+      <c r="H283" s="13">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I283" s="2" t="s">
@@ -11055,8 +11061,8 @@
       <c r="G284" s="2">
         <v>150000</v>
       </c>
-      <c r="H284" s="2">
-        <f>G284/1000</f>
+      <c r="H284" s="13">
+        <f t="shared" si="4"/>
         <v>150</v>
       </c>
       <c r="I284" s="2" t="s">
@@ -11091,8 +11097,8 @@
       <c r="G285" s="2">
         <v>75000</v>
       </c>
-      <c r="H285" s="2">
-        <f>G285/1000</f>
+      <c r="H285" s="13">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="I285" s="2" t="s">
@@ -11127,8 +11133,8 @@
       <c r="G286" s="2">
         <v>70000</v>
       </c>
-      <c r="H286" s="2">
-        <f>G286/1000</f>
+      <c r="H286" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I286" s="2" t="s">
@@ -11163,8 +11169,8 @@
       <c r="G287" s="2">
         <v>75000</v>
       </c>
-      <c r="H287" s="2">
-        <f>G287/1000</f>
+      <c r="H287" s="13">
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="I287" s="2" t="s">
@@ -11199,8 +11205,8 @@
       <c r="G288" s="2">
         <v>0</v>
       </c>
-      <c r="H288" s="2">
-        <f>G288/1000</f>
+      <c r="H288" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I288" s="2" t="s">
@@ -11235,8 +11241,8 @@
       <c r="G289" s="2">
         <v>0</v>
       </c>
-      <c r="H289" s="2">
-        <f>G289/1000</f>
+      <c r="H289" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I289" s="2" t="s">
@@ -11271,8 +11277,8 @@
       <c r="G290" s="2">
         <v>0</v>
       </c>
-      <c r="H290" s="2">
-        <f>G290/1000</f>
+      <c r="H290" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I290" s="2" t="s">
@@ -11307,8 +11313,8 @@
       <c r="G291" s="2">
         <v>0</v>
       </c>
-      <c r="H291" s="2">
-        <f>G291/1000</f>
+      <c r="H291" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I291" s="2" t="s">
@@ -11343,8 +11349,8 @@
       <c r="G292" s="2">
         <v>0</v>
       </c>
-      <c r="H292" s="2">
-        <f>G292/1000</f>
+      <c r="H292" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I292" s="2" t="s">
@@ -11379,8 +11385,8 @@
       <c r="G293" s="2">
         <v>0</v>
       </c>
-      <c r="H293" s="2">
-        <f>G293/1000</f>
+      <c r="H293" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I293" s="2" t="s">
@@ -11415,8 +11421,8 @@
       <c r="G294" s="2">
         <v>0</v>
       </c>
-      <c r="H294" s="2">
-        <f>G294/1000</f>
+      <c r="H294" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I294" s="2" t="s">
@@ -11451,8 +11457,8 @@
       <c r="G295" s="2">
         <v>0</v>
       </c>
-      <c r="H295" s="2">
-        <f>G295/1000</f>
+      <c r="H295" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I295" s="2" t="s">
@@ -11487,8 +11493,8 @@
       <c r="G296" s="2">
         <v>0</v>
       </c>
-      <c r="H296" s="2">
-        <f>G296/1000</f>
+      <c r="H296" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I296" s="2" t="s">
@@ -11523,8 +11529,8 @@
       <c r="G297" s="2">
         <v>140000</v>
       </c>
-      <c r="H297" s="2">
-        <f>G297/1000</f>
+      <c r="H297" s="13">
+        <f t="shared" si="4"/>
         <v>140</v>
       </c>
       <c r="I297" s="2" t="s">
@@ -11559,8 +11565,8 @@
       <c r="G298" s="2">
         <v>24600</v>
       </c>
-      <c r="H298" s="2">
-        <f>G298/1000</f>
+      <c r="H298" s="13">
+        <f t="shared" si="4"/>
         <v>24.6</v>
       </c>
       <c r="I298" s="2" t="s">
@@ -11595,8 +11601,8 @@
       <c r="G299" s="2">
         <v>44360</v>
       </c>
-      <c r="H299" s="2">
-        <f>G299/1000</f>
+      <c r="H299" s="13">
+        <f t="shared" si="4"/>
         <v>44.36</v>
       </c>
       <c r="I299" s="2" t="s">
@@ -11631,8 +11637,8 @@
       <c r="G300" s="2">
         <v>5000000</v>
       </c>
-      <c r="H300" s="2">
-        <f>G300/1000</f>
+      <c r="H300" s="13">
+        <f t="shared" si="4"/>
         <v>5000</v>
       </c>
       <c r="I300" s="2" t="s">
@@ -11667,8 +11673,8 @@
       <c r="G301" s="2">
         <v>25000</v>
       </c>
-      <c r="H301" s="2">
-        <f>G301/1000</f>
+      <c r="H301" s="13">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="I301" s="2" t="s">
@@ -11703,8 +11709,8 @@
       <c r="G302" s="2">
         <v>24600</v>
       </c>
-      <c r="H302" s="2">
-        <f>G302/1000</f>
+      <c r="H302" s="13">
+        <f t="shared" si="4"/>
         <v>24.6</v>
       </c>
       <c r="I302" s="2" t="s">
@@ -11739,8 +11745,8 @@
       <c r="G303" s="2">
         <v>70000</v>
       </c>
-      <c r="H303" s="2">
-        <f>G303/1000</f>
+      <c r="H303" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I303" s="2" t="s">
@@ -11775,8 +11781,8 @@
       <c r="G304" s="2">
         <v>70000</v>
       </c>
-      <c r="H304" s="2">
-        <f>G304/1000</f>
+      <c r="H304" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I304" s="2" t="s">
@@ -11811,8 +11817,8 @@
       <c r="G305" s="2">
         <v>70000</v>
       </c>
-      <c r="H305" s="2">
-        <f>G305/1000</f>
+      <c r="H305" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I305" s="2" t="s">
@@ -11847,8 +11853,8 @@
       <c r="G306" s="2">
         <v>4000</v>
       </c>
-      <c r="H306" s="2">
-        <f>G306/1000</f>
+      <c r="H306" s="13">
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="I306" s="2" t="s">
@@ -11883,8 +11889,8 @@
       <c r="G307" s="2">
         <v>22180</v>
       </c>
-      <c r="H307" s="2">
-        <f>G307/1000</f>
+      <c r="H307" s="13">
+        <f t="shared" si="4"/>
         <v>22.18</v>
       </c>
       <c r="I307" s="2" t="s">
@@ -11919,8 +11925,8 @@
       <c r="G308" s="2">
         <v>19250</v>
       </c>
-      <c r="H308" s="2">
-        <f>G308/1000</f>
+      <c r="H308" s="13">
+        <f t="shared" si="4"/>
         <v>19.25</v>
       </c>
       <c r="I308" s="2" t="s">
@@ -11955,8 +11961,8 @@
       <c r="G309" s="2">
         <v>0</v>
       </c>
-      <c r="H309" s="2">
-        <f>G309/1000</f>
+      <c r="H309" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I309" s="2" t="s">
@@ -11991,8 +11997,8 @@
       <c r="G310" s="2">
         <v>0</v>
       </c>
-      <c r="H310" s="2">
-        <f>G310/1000</f>
+      <c r="H310" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I310" s="2" t="s">
@@ -12027,8 +12033,8 @@
       <c r="G311" s="2">
         <v>0</v>
       </c>
-      <c r="H311" s="2">
-        <f>G311/1000</f>
+      <c r="H311" s="13">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I311" s="2" t="s">
@@ -12063,8 +12069,8 @@
       <c r="G312" s="2">
         <v>7335</v>
       </c>
-      <c r="H312" s="2">
-        <f>G312/1000</f>
+      <c r="H312" s="13">
+        <f t="shared" si="4"/>
         <v>7.335</v>
       </c>
       <c r="I312" s="2" t="s">
@@ -12099,8 +12105,8 @@
       <c r="G313" s="2">
         <v>7716</v>
       </c>
-      <c r="H313" s="2">
-        <f>G313/1000</f>
+      <c r="H313" s="13">
+        <f t="shared" si="4"/>
         <v>7.7160000000000002</v>
       </c>
       <c r="I313" s="2" t="s">
@@ -12135,8 +12141,8 @@
       <c r="G314" s="2">
         <v>22760</v>
       </c>
-      <c r="H314" s="2">
-        <f>G314/1000</f>
+      <c r="H314" s="13">
+        <f t="shared" si="4"/>
         <v>22.76</v>
       </c>
       <c r="I314" s="2" t="s">
@@ -12171,8 +12177,8 @@
       <c r="G315" s="2">
         <v>70000</v>
       </c>
-      <c r="H315" s="2">
-        <f>G315/1000</f>
+      <c r="H315" s="13">
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="I315" s="2" t="s">
@@ -12207,8 +12213,8 @@
       <c r="G316" s="2">
         <v>21113</v>
       </c>
-      <c r="H316" s="2">
-        <f>G316/1000</f>
+      <c r="H316" s="13">
+        <f t="shared" si="4"/>
         <v>21.113</v>
       </c>
       <c r="I316" s="2" t="s">
@@ -12243,8 +12249,8 @@
       <c r="G317" s="2">
         <v>9720</v>
       </c>
-      <c r="H317" s="2">
-        <f>G317/1000</f>
+      <c r="H317" s="13">
+        <f t="shared" si="4"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="I317" s="2" t="s">
@@ -12279,8 +12285,8 @@
       <c r="G318" s="2">
         <v>9720</v>
       </c>
-      <c r="H318" s="2">
-        <f>G318/1000</f>
+      <c r="H318" s="13">
+        <f t="shared" si="4"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="I318" s="2" t="s">
@@ -12315,8 +12321,8 @@
       <c r="G319" s="2">
         <v>87500</v>
       </c>
-      <c r="H319" s="2">
-        <f>G319/1000</f>
+      <c r="H319" s="13">
+        <f t="shared" si="4"/>
         <v>87.5</v>
       </c>
       <c r="I319" s="2" t="s">
@@ -12351,8 +12357,8 @@
       <c r="G320" s="2">
         <v>9720</v>
       </c>
-      <c r="H320" s="2">
-        <f>G320/1000</f>
+      <c r="H320" s="13">
+        <f t="shared" si="4"/>
         <v>9.7200000000000006</v>
       </c>
       <c r="I320" s="2" t="s">
@@ -12387,8 +12393,8 @@
       <c r="G321" s="2">
         <v>3600</v>
       </c>
-      <c r="H321" s="2">
-        <f>G321/1000</f>
+      <c r="H321" s="13">
+        <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
       <c r="I321" s="2" t="s">
@@ -12423,8 +12429,8 @@
       <c r="G322" s="2">
         <v>7797.6</v>
       </c>
-      <c r="H322" s="2">
-        <f>G322/1000</f>
+      <c r="H322" s="13">
+        <f t="shared" ref="H322:H385" si="5">G322/1000</f>
         <v>7.7976000000000001</v>
       </c>
       <c r="I322" s="2" t="s">
@@ -12459,8 +12465,8 @@
       <c r="G323" s="2">
         <v>4800</v>
       </c>
-      <c r="H323" s="2">
-        <f>G323/1000</f>
+      <c r="H323" s="13">
+        <f t="shared" si="5"/>
         <v>4.8</v>
       </c>
       <c r="I323" s="2" t="s">
@@ -12495,8 +12501,8 @@
       <c r="G324" s="2">
         <v>1500</v>
       </c>
-      <c r="H324" s="2">
-        <f>G324/1000</f>
+      <c r="H324" s="13">
+        <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="I324" s="2" t="s">
@@ -12531,8 +12537,8 @@
       <c r="G325" s="2">
         <v>10665</v>
       </c>
-      <c r="H325" s="2">
-        <f>G325/1000</f>
+      <c r="H325" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I325" s="2" t="s">
@@ -12567,8 +12573,8 @@
       <c r="G326" s="2">
         <v>10665</v>
       </c>
-      <c r="H326" s="2">
-        <f>G326/1000</f>
+      <c r="H326" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I326" s="2" t="s">
@@ -12603,8 +12609,8 @@
       <c r="G327" s="2">
         <v>8921.2999999999993</v>
       </c>
-      <c r="H327" s="2">
-        <f>G327/1000</f>
+      <c r="H327" s="13">
+        <f t="shared" si="5"/>
         <v>8.9212999999999987</v>
       </c>
       <c r="I327" s="2" t="s">
@@ -12639,8 +12645,8 @@
       <c r="G328" s="2">
         <v>10665</v>
       </c>
-      <c r="H328" s="2">
-        <f>G328/1000</f>
+      <c r="H328" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I328" s="2" t="s">
@@ -12675,8 +12681,8 @@
       <c r="G329" s="2">
         <v>5193</v>
       </c>
-      <c r="H329" s="2">
-        <f>G329/1000</f>
+      <c r="H329" s="13">
+        <f t="shared" si="5"/>
         <v>5.1929999999999996</v>
       </c>
       <c r="I329" s="2" t="s">
@@ -12711,8 +12717,8 @@
       <c r="G330" s="2">
         <v>93450</v>
       </c>
-      <c r="H330" s="2">
-        <f>G330/1000</f>
+      <c r="H330" s="13">
+        <f t="shared" si="5"/>
         <v>93.45</v>
       </c>
       <c r="I330" s="2" t="s">
@@ -12747,8 +12753,8 @@
       <c r="G331" s="2">
         <v>70070</v>
       </c>
-      <c r="H331" s="2">
-        <f>G331/1000</f>
+      <c r="H331" s="13">
+        <f t="shared" si="5"/>
         <v>70.069999999999993</v>
       </c>
       <c r="I331" s="2" t="s">
@@ -12783,8 +12789,8 @@
       <c r="G332" s="2">
         <v>8560</v>
       </c>
-      <c r="H332" s="2">
-        <f>G332/1000</f>
+      <c r="H332" s="13">
+        <f t="shared" si="5"/>
         <v>8.56</v>
       </c>
       <c r="I332" s="2" t="s">
@@ -12819,8 +12825,8 @@
       <c r="G333" s="2">
         <v>75000</v>
       </c>
-      <c r="H333" s="2">
-        <f>G333/1000</f>
+      <c r="H333" s="13">
+        <f t="shared" si="5"/>
         <v>75</v>
       </c>
       <c r="I333" s="2" t="s">
@@ -12855,8 +12861,8 @@
       <c r="G334" s="2">
         <v>70000</v>
       </c>
-      <c r="H334" s="2">
-        <f>G334/1000</f>
+      <c r="H334" s="13">
+        <f t="shared" si="5"/>
         <v>70</v>
       </c>
       <c r="I334" s="2" t="s">
@@ -12891,8 +12897,8 @@
       <c r="G335" s="2">
         <v>0</v>
       </c>
-      <c r="H335" s="2">
-        <f>G335/1000</f>
+      <c r="H335" s="13">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I335" s="2" t="s">
@@ -12927,8 +12933,8 @@
       <c r="G336" s="2">
         <v>19380</v>
       </c>
-      <c r="H336" s="2">
-        <f>G336/1000</f>
+      <c r="H336" s="13">
+        <f t="shared" si="5"/>
         <v>19.38</v>
       </c>
       <c r="I336" s="2" t="s">
@@ -12963,8 +12969,8 @@
       <c r="G337" s="2">
         <v>22400</v>
       </c>
-      <c r="H337" s="2">
-        <f>G337/1000</f>
+      <c r="H337" s="13">
+        <f t="shared" si="5"/>
         <v>22.4</v>
       </c>
       <c r="I337" s="2" t="s">
@@ -12999,8 +13005,8 @@
       <c r="G338" s="2">
         <v>10665</v>
       </c>
-      <c r="H338" s="2">
-        <f>G338/1000</f>
+      <c r="H338" s="13">
+        <f t="shared" si="5"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I338" s="2" t="s">
@@ -13035,8 +13041,8 @@
       <c r="G339" s="2">
         <v>210000</v>
       </c>
-      <c r="H339" s="2">
-        <f>G339/1000</f>
+      <c r="H339" s="13">
+        <f t="shared" si="5"/>
         <v>210</v>
       </c>
       <c r="I339" s="2" t="s">
@@ -13071,8 +13077,8 @@
       <c r="G340" s="2">
         <v>20480</v>
       </c>
-      <c r="H340" s="2">
-        <f>G340/1000</f>
+      <c r="H340" s="13">
+        <f t="shared" si="5"/>
         <v>20.48</v>
       </c>
       <c r="I340" s="2" t="s">
@@ -13107,7 +13113,7 @@
       <c r="G341" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H341" s="2">
+      <c r="H341" s="13">
         <v>7.6</v>
       </c>
       <c r="I341" s="2" t="s">
@@ -13142,8 +13148,8 @@
       <c r="G342" s="2">
         <v>70000</v>
       </c>
-      <c r="H342" s="2">
-        <f>G342/1000</f>
+      <c r="H342" s="13">
+        <f t="shared" ref="H342:H367" si="6">G342/1000</f>
         <v>70</v>
       </c>
       <c r="I342" s="2" t="s">
@@ -13178,8 +13184,8 @@
       <c r="G343" s="2">
         <v>70000</v>
       </c>
-      <c r="H343" s="2">
-        <f>G343/1000</f>
+      <c r="H343" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I343" s="2" t="s">
@@ -13214,8 +13220,8 @@
       <c r="G344" s="2">
         <v>210000</v>
       </c>
-      <c r="H344" s="2">
-        <f>G344/1000</f>
+      <c r="H344" s="13">
+        <f t="shared" si="6"/>
         <v>210</v>
       </c>
       <c r="I344" s="2" t="s">
@@ -13250,8 +13256,8 @@
       <c r="G345" s="2">
         <v>93380</v>
       </c>
-      <c r="H345" s="2">
-        <f>G345/1000</f>
+      <c r="H345" s="13">
+        <f t="shared" si="6"/>
         <v>93.38</v>
       </c>
       <c r="I345" s="2" t="s">
@@ -13286,8 +13292,8 @@
       <c r="G346" s="2">
         <v>64120</v>
       </c>
-      <c r="H346" s="2">
-        <f>G346/1000</f>
+      <c r="H346" s="13">
+        <f t="shared" si="6"/>
         <v>64.12</v>
       </c>
       <c r="I346" s="2" t="s">
@@ -13322,8 +13328,8 @@
       <c r="G347" s="2">
         <v>4500</v>
       </c>
-      <c r="H347" s="2">
-        <f>G347/1000</f>
+      <c r="H347" s="13">
+        <f t="shared" si="6"/>
         <v>4.5</v>
       </c>
       <c r="I347" s="2" t="s">
@@ -13358,8 +13364,8 @@
       <c r="G348" s="2">
         <v>10692.65</v>
       </c>
-      <c r="H348" s="2">
-        <f>G348/1000</f>
+      <c r="H348" s="13">
+        <f t="shared" si="6"/>
         <v>10.69265</v>
       </c>
       <c r="I348" s="2" t="s">
@@ -13394,8 +13400,8 @@
       <c r="G349" s="2">
         <v>140000</v>
       </c>
-      <c r="H349" s="2">
-        <f>G349/1000</f>
+      <c r="H349" s="13">
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="I349" s="2" t="s">
@@ -13430,8 +13436,8 @@
       <c r="G350" s="2">
         <v>10844.2</v>
       </c>
-      <c r="H350" s="2">
-        <f>G350/1000</f>
+      <c r="H350" s="13">
+        <f t="shared" si="6"/>
         <v>10.844200000000001</v>
       </c>
       <c r="I350" s="2" t="s">
@@ -13466,8 +13472,8 @@
       <c r="G351" s="2">
         <v>9602.7999999999993</v>
       </c>
-      <c r="H351" s="2">
-        <f>G351/1000</f>
+      <c r="H351" s="13">
+        <f t="shared" si="6"/>
         <v>9.6027999999999984</v>
       </c>
       <c r="I351" s="2" t="s">
@@ -13502,8 +13508,8 @@
       <c r="G352" s="2">
         <v>140000</v>
       </c>
-      <c r="H352" s="2">
-        <f>G352/1000</f>
+      <c r="H352" s="13">
+        <f t="shared" si="6"/>
         <v>140</v>
       </c>
       <c r="I352" s="2" t="s">
@@ -13538,8 +13544,8 @@
       <c r="G353" s="2">
         <v>70000</v>
       </c>
-      <c r="H353" s="2">
-        <f>G353/1000</f>
+      <c r="H353" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I353" s="2" t="s">
@@ -13574,8 +13580,8 @@
       <c r="G354" s="2">
         <v>10665</v>
       </c>
-      <c r="H354" s="2">
-        <f>G354/1000</f>
+      <c r="H354" s="13">
+        <f t="shared" si="6"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I354" s="2" t="s">
@@ -13610,8 +13616,8 @@
       <c r="G355" s="2">
         <v>70000</v>
       </c>
-      <c r="H355" s="2">
-        <f>G355/1000</f>
+      <c r="H355" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I355" s="2" t="s">
@@ -13646,8 +13652,8 @@
       <c r="G356" s="2">
         <v>18960</v>
       </c>
-      <c r="H356" s="2">
-        <f>G356/1000</f>
+      <c r="H356" s="13">
+        <f t="shared" si="6"/>
         <v>18.96</v>
       </c>
       <c r="I356" s="2" t="s">
@@ -13682,8 +13688,8 @@
       <c r="G357" s="2">
         <v>70000</v>
       </c>
-      <c r="H357" s="2">
-        <f>G357/1000</f>
+      <c r="H357" s="13">
+        <f t="shared" si="6"/>
         <v>70</v>
       </c>
       <c r="I357" s="2" t="s">
@@ -13718,8 +13724,8 @@
       <c r="G358" s="2">
         <v>20050.599999999999</v>
       </c>
-      <c r="H358" s="2">
-        <f>G358/1000</f>
+      <c r="H358" s="13">
+        <f t="shared" si="6"/>
         <v>20.050599999999999</v>
       </c>
       <c r="I358" s="2" t="s">
@@ -13754,8 +13760,8 @@
       <c r="G359" s="2">
         <v>10554.18</v>
       </c>
-      <c r="H359" s="2">
-        <f>G359/1000</f>
+      <c r="H359" s="13">
+        <f t="shared" si="6"/>
         <v>10.554180000000001</v>
       </c>
       <c r="I359" s="2" t="s">
@@ -13790,8 +13796,8 @@
       <c r="G360" s="2">
         <v>7044.75</v>
       </c>
-      <c r="H360" s="2">
-        <f>G360/1000</f>
+      <c r="H360" s="13">
+        <f t="shared" si="6"/>
         <v>7.0447499999999996</v>
       </c>
       <c r="I360" s="2" t="s">
@@ -13826,8 +13832,8 @@
       <c r="G361" s="2">
         <v>50000</v>
       </c>
-      <c r="H361" s="2">
-        <f>G361/1000</f>
+      <c r="H361" s="13">
+        <f t="shared" si="6"/>
         <v>50</v>
       </c>
       <c r="I361" s="2" t="s">
@@ -13862,8 +13868,8 @@
       <c r="G362" s="2">
         <v>26000</v>
       </c>
-      <c r="H362" s="2">
-        <f>G362/1000</f>
+      <c r="H362" s="13">
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
       <c r="I362" s="2" t="s">
@@ -13898,8 +13904,8 @@
       <c r="G363" s="2">
         <v>9620</v>
       </c>
-      <c r="H363" s="2">
-        <f>G363/1000</f>
+      <c r="H363" s="13">
+        <f t="shared" si="6"/>
         <v>9.6199999999999992</v>
       </c>
       <c r="I363" s="2" t="s">
@@ -13934,8 +13940,8 @@
       <c r="G364" s="2">
         <v>125000</v>
       </c>
-      <c r="H364" s="2">
-        <f>G364/1000</f>
+      <c r="H364" s="13">
+        <f t="shared" si="6"/>
         <v>125</v>
       </c>
       <c r="I364" s="2" t="s">
@@ -13970,8 +13976,8 @@
       <c r="G365" s="2">
         <v>10665</v>
       </c>
-      <c r="H365" s="2">
-        <f>G365/1000</f>
+      <c r="H365" s="13">
+        <f t="shared" si="6"/>
         <v>10.664999999999999</v>
       </c>
       <c r="I365" s="2" t="s">
@@ -14006,8 +14012,8 @@
       <c r="G366" s="2">
         <v>9065.25</v>
       </c>
-      <c r="H366" s="2">
-        <f>G366/1000</f>
+      <c r="H366" s="13">
+        <f t="shared" si="6"/>
         <v>9.0652500000000007</v>
       </c>
       <c r="I366" s="2" t="s">
@@ -14042,8 +14048,8 @@
       <c r="G367" s="2">
         <v>150000</v>
       </c>
-      <c r="H367" s="2">
-        <f>G367/1000</f>
+      <c r="H367" s="13">
+        <f t="shared" si="6"/>
         <v>150</v>
       </c>
       <c r="I367" s="2" t="s">
@@ -14053,14 +14059,79 @@
         <v>0</v>
       </c>
       <c r="K367" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368" s="5">
+        <v>46106</v>
+      </c>
+      <c r="C368" t="s">
+        <v>7</v>
+      </c>
+      <c r="D368" t="s">
+        <v>55</v>
+      </c>
+      <c r="E368" s="2">
+        <v>3</v>
+      </c>
+      <c r="F368" t="s">
+        <v>90</v>
+      </c>
+      <c r="H368" s="13">
+        <v>75</v>
+      </c>
+      <c r="I368" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J368">
+        <v>0</v>
+      </c>
+      <c r="K368" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369" s="5">
+        <v>46106</v>
+      </c>
+      <c r="C369" t="s">
+        <v>7</v>
+      </c>
+      <c r="D369" t="s">
+        <v>55</v>
+      </c>
+      <c r="E369" s="2">
+        <v>3</v>
+      </c>
+      <c r="F369" t="s">
+        <v>90</v>
+      </c>
+      <c r="H369" s="13">
+        <v>75</v>
+      </c>
+      <c r="I369" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369" s="12">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372F96D2-81BB-4DAD-AE01-98441BB125B2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FB7A1D-6B3C-410E-B378-7A20E2DB5588}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="93">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -299,6 +299,12 @@
   <si>
     <t xml:space="preserve">Frijol Mungo </t>
   </si>
+  <si>
+    <t xml:space="preserve">café verde </t>
+  </si>
+  <si>
+    <t xml:space="preserve">café vede </t>
+  </si>
 </sst>
 </file>
 
@@ -398,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -431,13 +437,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -447,6 +453,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -499,8 +506,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J369" totalsRowShown="0" totalsRowDxfId="10">
-  <autoFilter ref="A1:J369" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J371" totalsRowShown="0" totalsRowDxfId="10">
+  <autoFilter ref="A1:J371" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
     <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="8"/>
@@ -509,10 +516,10 @@
     <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="7" totalsRowDxfId="6"/>
     <tableColumn id="18" xr3:uid="{33E6F7D3-8F24-4F60-BCE9-4590974B7832}" name="CONTENIDO"/>
     <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" dataDxfId="0" totalsRowDxfId="3">
+    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>G2/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="2" totalsRowDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="1" totalsRowDxfId="0"/>
     <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -836,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:K369"/>
+  <dimension ref="A1:K371"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -12430,7 +12437,7 @@
         <v>7797.6</v>
       </c>
       <c r="H322" s="13">
-        <f t="shared" ref="H322:H385" si="5">G322/1000</f>
+        <f t="shared" ref="H322:H340" si="5">G322/1000</f>
         <v>7.7976000000000001</v>
       </c>
       <c r="I322" s="2" t="s">
@@ -14123,6 +14130,70 @@
         <v>0</v>
       </c>
       <c r="K369" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370" s="5">
+        <v>46107</v>
+      </c>
+      <c r="C370" t="s">
+        <v>7</v>
+      </c>
+      <c r="D370" t="s">
+        <v>8</v>
+      </c>
+      <c r="E370" s="2">
+        <v>3</v>
+      </c>
+      <c r="F370" t="s">
+        <v>91</v>
+      </c>
+      <c r="H370" s="13">
+        <v>70</v>
+      </c>
+      <c r="I370" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J370">
+        <v>0</v>
+      </c>
+      <c r="K370" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371" s="5">
+        <v>46107</v>
+      </c>
+      <c r="C371" t="s">
+        <v>7</v>
+      </c>
+      <c r="D371" t="s">
+        <v>8</v>
+      </c>
+      <c r="E371" s="2">
+        <v>3</v>
+      </c>
+      <c r="F371" t="s">
+        <v>92</v>
+      </c>
+      <c r="H371" s="13">
+        <v>70</v>
+      </c>
+      <c r="I371" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371" s="14">
         <v>0</v>
       </c>
     </row>

--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FB7A1D-6B3C-410E-B378-7A20E2DB5588}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB81D984-D770-421C-BE14-68F743ED41DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -447,6 +447,17 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -460,16 +471,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -506,21 +507,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J371" totalsRowShown="0" totalsRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J372" totalsRowCount="1" totalsRowDxfId="10">
   <autoFilter ref="A1:J371" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
-    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="4"/>
     <tableColumn id="6" xr3:uid="{66D4B823-3C30-44D5-A641-20D7BF6E166A}" name="TIPO DE CARGA"/>
     <tableColumn id="7" xr3:uid="{C3650C10-5CB4-45A7-9736-6A80A51D6F83}" name="TIPO DE SERVICIO"/>
-    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="15" xr3:uid="{99B5645B-5CD8-4042-833E-BE48D00BC86E}" name="LLENOS RECIBIDOS (EXPORTADOS)" dataDxfId="8" totalsRowDxfId="3"/>
     <tableColumn id="18" xr3:uid="{33E6F7D3-8F24-4F60-BCE9-4590974B7832}" name="CONTENIDO"/>
-    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="21" xr3:uid="{D64B384B-46A0-483C-8C32-5474495F7791}" name="Peso Neto Exportado" dataDxfId="7" totalsRowDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{D32BEFD5-B821-4C9D-9A95-EA7B65F72C1A}" name="Peso Neto Exportado2" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="1">
       <calculatedColumnFormula>G2/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="1" totalsRowDxfId="0"/>
-    <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado "/>
+    <tableColumn id="22" xr3:uid="{CD599142-04A2-4632-8A98-CA3F9CF4F273}" name="DESTINO " dataDxfId="5" totalsRowDxfId="0"/>
+    <tableColumn id="23" xr3:uid="{2EDED6B6-E583-4F20-89DA-9AA2F9B82EE1}" name="Peso Neto Importado " totalsRowFunction="custom">
+      <totalsRowFormula>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</totalsRowFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -843,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:K371"/>
+  <dimension ref="A1:K372"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -14197,6 +14200,21 @@
         <v>0</v>
       </c>
     </row>
+    <row r="372" spans="1:11">
+      <c r="B372" s="5"/>
+      <c r="H372" s="13">
+        <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
+        <v>34543.928000000022</v>
+      </c>
+      <c r="J372">
+        <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
+        <v>134.994</v>
+      </c>
+      <c r="K372">
+        <f>SUM(K2:K371)/1000</f>
+        <v>1494.36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB81D984-D770-421C-BE14-68F743ED41DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9754DB4-900F-4A0B-AD89-A693A9A1BCA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="95">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -305,6 +305,12 @@
   <si>
     <t xml:space="preserve">café vede </t>
   </si>
+  <si>
+    <t>REPUBLICA CHECA</t>
+  </si>
+  <si>
+    <t>RUSIA</t>
+  </si>
 </sst>
 </file>
 
@@ -507,8 +513,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J372" totalsRowCount="1" totalsRowDxfId="10">
-  <autoFilter ref="A1:J371" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J376" totalsRowCount="1" totalsRowDxfId="10">
+  <autoFilter ref="A1:J375" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
     <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="4"/>
@@ -846,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:K372"/>
+  <dimension ref="A1:K376"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -14201,16 +14207,144 @@
       </c>
     </row>
     <row r="372" spans="1:11">
-      <c r="B372" s="5"/>
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372" s="5">
+        <v>46120</v>
+      </c>
+      <c r="C372" t="s">
+        <v>7</v>
+      </c>
+      <c r="D372" t="s">
+        <v>8</v>
+      </c>
+      <c r="E372" s="2">
+        <v>1</v>
+      </c>
+      <c r="F372" t="s">
+        <v>23</v>
+      </c>
       <c r="H372" s="13">
+        <v>19380</v>
+      </c>
+      <c r="I372" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373" s="5">
+        <v>46120</v>
+      </c>
+      <c r="C373" t="s">
+        <v>7</v>
+      </c>
+      <c r="D373" t="s">
+        <v>55</v>
+      </c>
+      <c r="E373" s="2">
+        <v>2</v>
+      </c>
+      <c r="F373" t="s">
+        <v>9</v>
+      </c>
+      <c r="H373" s="13">
+        <v>50000</v>
+      </c>
+      <c r="I373" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J373">
+        <v>0</v>
+      </c>
+      <c r="K373" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374" s="5">
+        <v>46121</v>
+      </c>
+      <c r="C374" t="s">
+        <v>7</v>
+      </c>
+      <c r="D374" t="s">
+        <v>8</v>
+      </c>
+      <c r="E374" s="2">
+        <v>1</v>
+      </c>
+      <c r="F374" t="s">
+        <v>23</v>
+      </c>
+      <c r="H374" s="13">
+        <v>28420</v>
+      </c>
+      <c r="I374" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J374">
+        <v>0</v>
+      </c>
+      <c r="K374" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375" s="5">
+        <v>46121</v>
+      </c>
+      <c r="C375" t="s">
+        <v>7</v>
+      </c>
+      <c r="D375" t="s">
+        <v>55</v>
+      </c>
+      <c r="E375" s="2">
+        <v>1</v>
+      </c>
+      <c r="F375" t="s">
+        <v>77</v>
+      </c>
+      <c r="H375" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I375" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J375">
+        <v>0</v>
+      </c>
+      <c r="K375" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11">
+      <c r="B376" s="5"/>
+      <c r="H376" s="13">
         <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
-        <v>34543.928000000022</v>
-      </c>
-      <c r="J372">
+        <v>143008.92800000001</v>
+      </c>
+      <c r="J376">
         <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
         <v>134.994</v>
       </c>
-      <c r="K372">
+      <c r="K376">
         <f>SUM(K2:K371)/1000</f>
         <v>1494.36</v>
       </c>

--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9754DB4-900F-4A0B-AD89-A693A9A1BCA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12997FE4-2A65-428B-8FA9-DD4DCD8D4ABA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="7470" windowHeight="8640" tabRatio="906" xr2:uid="{7D6B2630-CDD6-4E4F-8803-3B7521F27F6B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="106">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -311,6 +311,39 @@
   <si>
     <t>RUSIA</t>
   </si>
+  <si>
+    <t>NO CONTENERIZADA (AEREA)</t>
+  </si>
+  <si>
+    <t>TAUREL</t>
+  </si>
+  <si>
+    <t>FIRST INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>BARRAEZ &amp; ASOC.</t>
+  </si>
+  <si>
+    <t>FIRST INTERNATIONAL TRANSPORT</t>
+  </si>
+  <si>
+    <t>CHINA</t>
+  </si>
+  <si>
+    <t>PERU</t>
+  </si>
+  <si>
+    <t>PAISES BAJOS</t>
+  </si>
+  <si>
+    <t>4998.00</t>
+  </si>
+  <si>
+    <t>9834.00</t>
+  </si>
+  <si>
+    <t>5440.00</t>
+  </si>
 </sst>
 </file>
 
@@ -410,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -444,6 +477,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,8 +547,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J376" totalsRowCount="1" totalsRowDxfId="10">
-  <autoFilter ref="A1:J375" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}" name="Tabla1" displayName="Tabla1" ref="A1:J407" totalsRowCount="1" totalsRowDxfId="10">
+  <autoFilter ref="A1:J406" xr:uid="{340BE8A2-A3CB-45AB-8842-D903877EA22B}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{8E80F481-58A9-4EF5-9BD3-4DE99E71B7AE}" name="N° DE OPERACIÓN"/>
     <tableColumn id="5" xr3:uid="{59A9AB34-6356-455A-B8FD-E74723C9892D}" name="FECHA" dataDxfId="9" totalsRowDxfId="4"/>
@@ -852,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C559613-914B-4B50-8C5B-99B98A1D93DC}">
-  <dimension ref="A1:K376"/>
+  <dimension ref="A1:K407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -14335,18 +14369,885 @@
       </c>
     </row>
     <row r="376" spans="1:11">
-      <c r="B376" s="5"/>
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376" s="5">
+        <v>46126</v>
+      </c>
+      <c r="C376" t="s">
+        <v>7</v>
+      </c>
+      <c r="D376" t="s">
+        <v>55</v>
+      </c>
+      <c r="E376" s="2">
+        <v>2</v>
+      </c>
+      <c r="F376" t="s">
+        <v>96</v>
+      </c>
       <c r="H376" s="13">
-        <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
-        <v>143008.92800000001</v>
-      </c>
-      <c r="J376">
-        <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
-        <v>134.994</v>
-      </c>
-      <c r="K376">
+        <v>41340</v>
+      </c>
+      <c r="I376" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J376" s="2">
+        <v>0</v>
+      </c>
+      <c r="K376" s="15"/>
+    </row>
+    <row r="377" spans="1:11">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C377" t="s">
+        <v>7</v>
+      </c>
+      <c r="D377" t="s">
+        <v>55</v>
+      </c>
+      <c r="F377" t="s">
+        <v>96</v>
+      </c>
+      <c r="I377" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J377" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K377" s="15"/>
+    </row>
+    <row r="378" spans="1:11">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C378" t="s">
+        <v>7</v>
+      </c>
+      <c r="D378" t="s">
+        <v>55</v>
+      </c>
+      <c r="F378" t="s">
+        <v>96</v>
+      </c>
+      <c r="I378" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J378" s="2">
+        <v>44229</v>
+      </c>
+      <c r="K378" s="15"/>
+    </row>
+    <row r="379" spans="1:11">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C379" t="s">
+        <v>7</v>
+      </c>
+      <c r="D379" t="s">
+        <v>55</v>
+      </c>
+      <c r="F379" t="s">
+        <v>96</v>
+      </c>
+      <c r="I379" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J379" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K379" s="15"/>
+    </row>
+    <row r="380" spans="1:11">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380" s="5">
+        <v>46127</v>
+      </c>
+      <c r="C380" t="s">
+        <v>7</v>
+      </c>
+      <c r="D380" t="s">
+        <v>55</v>
+      </c>
+      <c r="F380" t="s">
+        <v>96</v>
+      </c>
+      <c r="I380" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J380" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K380">
         <f>SUM(K2:K371)/1000</f>
         <v>1494.36</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C381" t="s">
+        <v>7</v>
+      </c>
+      <c r="D381" t="s">
+        <v>55</v>
+      </c>
+      <c r="E381" s="2">
+        <v>1</v>
+      </c>
+      <c r="F381" t="s">
+        <v>97</v>
+      </c>
+      <c r="H381" s="13">
+        <v>8337</v>
+      </c>
+      <c r="I381" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J381" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C382" t="s">
+        <v>7</v>
+      </c>
+      <c r="D382" t="s">
+        <v>55</v>
+      </c>
+      <c r="E382" s="2">
+        <v>1</v>
+      </c>
+      <c r="F382" t="s">
+        <v>97</v>
+      </c>
+      <c r="H382" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I382" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J382" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="1:11">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383" s="5">
+        <v>46134</v>
+      </c>
+      <c r="C383" t="s">
+        <v>7</v>
+      </c>
+      <c r="D383" t="s">
+        <v>55</v>
+      </c>
+      <c r="E383" s="2">
+        <v>4</v>
+      </c>
+      <c r="F383" t="s">
+        <v>97</v>
+      </c>
+      <c r="H383" s="13">
+        <v>100000</v>
+      </c>
+      <c r="I383" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J383" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384" s="5">
+        <v>46139</v>
+      </c>
+      <c r="C384" t="s">
+        <v>7</v>
+      </c>
+      <c r="D384" t="s">
+        <v>55</v>
+      </c>
+      <c r="E384" s="2">
+        <v>1</v>
+      </c>
+      <c r="F384" t="s">
+        <v>97</v>
+      </c>
+      <c r="H384" s="13">
+        <v>9290</v>
+      </c>
+      <c r="I384" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J384" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:10">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385" s="5">
+        <v>46139</v>
+      </c>
+      <c r="C385" t="s">
+        <v>7</v>
+      </c>
+      <c r="D385" t="s">
+        <v>55</v>
+      </c>
+      <c r="E385" s="2">
+        <v>1</v>
+      </c>
+      <c r="F385" t="s">
+        <v>97</v>
+      </c>
+      <c r="H385" s="13">
+        <v>8560</v>
+      </c>
+      <c r="I385" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J385" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:10">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386" s="5">
+        <v>46140</v>
+      </c>
+      <c r="C386" t="s">
+        <v>7</v>
+      </c>
+      <c r="D386" t="s">
+        <v>55</v>
+      </c>
+      <c r="E386" s="2">
+        <v>1</v>
+      </c>
+      <c r="F386" t="s">
+        <v>97</v>
+      </c>
+      <c r="H386" s="13">
+        <v>8652</v>
+      </c>
+      <c r="I386" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J386" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:10">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387" s="5">
+        <v>46149</v>
+      </c>
+      <c r="C387" t="s">
+        <v>7</v>
+      </c>
+      <c r="D387" t="s">
+        <v>55</v>
+      </c>
+      <c r="E387" s="2">
+        <v>1</v>
+      </c>
+      <c r="F387" t="s">
+        <v>96</v>
+      </c>
+      <c r="H387" s="13">
+        <v>11520</v>
+      </c>
+      <c r="I387" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J387" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:10">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388" s="5">
+        <v>45790</v>
+      </c>
+      <c r="C388" t="s">
+        <v>7</v>
+      </c>
+      <c r="D388" t="s">
+        <v>55</v>
+      </c>
+      <c r="E388" s="2">
+        <v>1</v>
+      </c>
+      <c r="F388" t="s">
+        <v>97</v>
+      </c>
+      <c r="H388" s="13">
+        <v>9447.5</v>
+      </c>
+      <c r="I388" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J388" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:10">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389" s="5">
+        <v>46156</v>
+      </c>
+      <c r="C389" t="s">
+        <v>7</v>
+      </c>
+      <c r="D389" t="s">
+        <v>55</v>
+      </c>
+      <c r="E389" s="2">
+        <v>3</v>
+      </c>
+      <c r="F389" t="s">
+        <v>96</v>
+      </c>
+      <c r="H389" s="13">
+        <v>0</v>
+      </c>
+      <c r="I389" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J389" s="2">
+        <v>52995.600000000006</v>
+      </c>
+    </row>
+    <row r="390" spans="1:10">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390" s="5">
+        <v>46156</v>
+      </c>
+      <c r="C390" t="s">
+        <v>7</v>
+      </c>
+      <c r="D390" t="s">
+        <v>55</v>
+      </c>
+      <c r="E390" s="2">
+        <v>3</v>
+      </c>
+      <c r="F390" t="s">
+        <v>96</v>
+      </c>
+      <c r="H390" s="13">
+        <v>0</v>
+      </c>
+      <c r="I390" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J390" s="2">
+        <v>52995.600000000006</v>
+      </c>
+    </row>
+    <row r="391" spans="1:10">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391" s="5">
+        <v>46157</v>
+      </c>
+      <c r="C391" t="s">
+        <v>7</v>
+      </c>
+      <c r="D391" t="s">
+        <v>55</v>
+      </c>
+      <c r="E391" s="2">
+        <v>1</v>
+      </c>
+      <c r="F391" t="s">
+        <v>96</v>
+      </c>
+      <c r="H391" s="13">
+        <v>0</v>
+      </c>
+      <c r="I391" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J391" s="2">
+        <v>4356</v>
+      </c>
+    </row>
+    <row r="392" spans="1:10">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392" s="5">
+        <v>46157</v>
+      </c>
+      <c r="C392" t="s">
+        <v>95</v>
+      </c>
+      <c r="D392" t="s">
+        <v>55</v>
+      </c>
+      <c r="F392" t="s">
+        <v>97</v>
+      </c>
+      <c r="H392" s="13">
+        <v>1175</v>
+      </c>
+      <c r="I392" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J392" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:10">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393" s="5">
+        <v>46169</v>
+      </c>
+      <c r="C393" t="s">
+        <v>7</v>
+      </c>
+      <c r="D393" t="s">
+        <v>55</v>
+      </c>
+      <c r="E393" s="2">
+        <v>1</v>
+      </c>
+      <c r="F393" t="s">
+        <v>97</v>
+      </c>
+      <c r="H393" s="13">
+        <v>8500</v>
+      </c>
+      <c r="I393" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J393" s="2"/>
+    </row>
+    <row r="394" spans="1:10">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394" s="5">
+        <v>46169</v>
+      </c>
+      <c r="C394" t="s">
+        <v>7</v>
+      </c>
+      <c r="D394" t="s">
+        <v>55</v>
+      </c>
+      <c r="E394" s="2">
+        <v>1</v>
+      </c>
+      <c r="F394" t="s">
+        <v>97</v>
+      </c>
+      <c r="H394" s="13">
+        <v>9718</v>
+      </c>
+      <c r="I394" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J394" s="2"/>
+    </row>
+    <row r="395" spans="1:10">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395" s="5">
+        <v>46170</v>
+      </c>
+      <c r="C395" t="s">
+        <v>7</v>
+      </c>
+      <c r="D395" t="s">
+        <v>55</v>
+      </c>
+      <c r="E395" s="2">
+        <v>1</v>
+      </c>
+      <c r="F395" t="s">
+        <v>97</v>
+      </c>
+      <c r="H395" s="13">
+        <v>10340</v>
+      </c>
+      <c r="I395" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J395" s="2"/>
+    </row>
+    <row r="396" spans="1:10">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396" s="5">
+        <v>46176</v>
+      </c>
+      <c r="C396" t="s">
+        <v>7</v>
+      </c>
+      <c r="D396" t="s">
+        <v>55</v>
+      </c>
+      <c r="E396" s="2">
+        <v>2</v>
+      </c>
+      <c r="F396" t="s">
+        <v>98</v>
+      </c>
+      <c r="H396" s="13">
+        <v>46000</v>
+      </c>
+      <c r="I396" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J396" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:10">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397" s="5">
+        <v>46178</v>
+      </c>
+      <c r="C397" t="s">
+        <v>7</v>
+      </c>
+      <c r="D397" t="s">
+        <v>8</v>
+      </c>
+      <c r="E397" s="2">
+        <v>1</v>
+      </c>
+      <c r="F397" t="s">
+        <v>98</v>
+      </c>
+      <c r="H397" s="13">
+        <v>25340</v>
+      </c>
+      <c r="I397" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J397" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:10">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398" s="5">
+        <v>46178</v>
+      </c>
+      <c r="C398" t="s">
+        <v>7</v>
+      </c>
+      <c r="D398" t="s">
+        <v>55</v>
+      </c>
+      <c r="F398" t="s">
+        <v>96</v>
+      </c>
+      <c r="H398" s="13">
+        <v>0</v>
+      </c>
+      <c r="I398" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J398" s="2">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="399" spans="1:10">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C399" t="s">
+        <v>7</v>
+      </c>
+      <c r="D399" t="s">
+        <v>8</v>
+      </c>
+      <c r="E399" s="2">
+        <v>1</v>
+      </c>
+      <c r="F399" t="s">
+        <v>99</v>
+      </c>
+      <c r="H399" s="13">
+        <v>19200</v>
+      </c>
+      <c r="I399" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J399" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:10">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C400" t="s">
+        <v>7</v>
+      </c>
+      <c r="D400" t="s">
+        <v>55</v>
+      </c>
+      <c r="E400" s="2">
+        <v>1</v>
+      </c>
+      <c r="F400" t="s">
+        <v>99</v>
+      </c>
+      <c r="H400" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I400" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J400" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:10">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401" s="5">
+        <v>46183</v>
+      </c>
+      <c r="C401" t="s">
+        <v>7</v>
+      </c>
+      <c r="D401" t="s">
+        <v>55</v>
+      </c>
+      <c r="E401" s="2">
+        <v>1</v>
+      </c>
+      <c r="F401" t="s">
+        <v>99</v>
+      </c>
+      <c r="H401" s="13">
+        <v>10665</v>
+      </c>
+      <c r="I401" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J401" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:10">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C402" t="s">
+        <v>7</v>
+      </c>
+      <c r="D402" t="s">
+        <v>8</v>
+      </c>
+      <c r="E402" s="2">
+        <v>1</v>
+      </c>
+      <c r="F402" t="s">
+        <v>98</v>
+      </c>
+      <c r="H402" s="13">
+        <v>28420</v>
+      </c>
+      <c r="I402" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J402" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:10">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C403" t="s">
+        <v>7</v>
+      </c>
+      <c r="D403" t="s">
+        <v>8</v>
+      </c>
+      <c r="E403" s="2">
+        <v>1</v>
+      </c>
+      <c r="F403" t="s">
+        <v>98</v>
+      </c>
+      <c r="H403" s="13">
+        <v>28420</v>
+      </c>
+      <c r="I403" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J403" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:10">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C404" t="s">
+        <v>7</v>
+      </c>
+      <c r="D404" t="s">
+        <v>55</v>
+      </c>
+      <c r="E404" s="2">
+        <v>1</v>
+      </c>
+      <c r="F404" t="s">
+        <v>99</v>
+      </c>
+      <c r="H404" s="13">
+        <v>8304</v>
+      </c>
+      <c r="I404" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J404" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="1:10">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405" s="5">
+        <v>46184</v>
+      </c>
+      <c r="C405" t="s">
+        <v>7</v>
+      </c>
+      <c r="D405" t="s">
+        <v>55</v>
+      </c>
+      <c r="E405" s="2">
+        <v>1</v>
+      </c>
+      <c r="F405" t="s">
+        <v>99</v>
+      </c>
+      <c r="H405" s="13">
+        <v>3510</v>
+      </c>
+      <c r="I405" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J405" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="1:10">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406" s="5">
+        <v>45825</v>
+      </c>
+      <c r="C406" t="s">
+        <v>7</v>
+      </c>
+      <c r="D406" t="s">
+        <v>55</v>
+      </c>
+      <c r="E406" s="2">
+        <v>1</v>
+      </c>
+      <c r="F406" t="s">
+        <v>96</v>
+      </c>
+      <c r="H406" s="13">
+        <v>9000</v>
+      </c>
+      <c r="I406" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J406" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="1:10">
+      <c r="B407" s="5"/>
+      <c r="H407" s="13">
+        <f>SUBTOTAL(109,Tabla1[Peso Neto Exportado2])</f>
+        <v>570077.42800000007</v>
+      </c>
+      <c r="J407">
+        <f>SUBTOTAL(109,Tabla1[[Peso Neto Importado ]])/1000</f>
+        <v>291.99020000000002</v>
       </c>
     </row>
   </sheetData>

--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B611CDD5-81AF-43BA-8759-FA67F57FD899}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCCAFFC-025F-4BBE-9039-37A8955EFF04}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8805" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="109">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -604,8 +604,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:J435" totalsRowCount="1">
-  <autoFilter ref="A1:J434" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:J437" totalsRowCount="1">
+  <autoFilter ref="A1:J436" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="N° DE OPERACIÓN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA" totalsRowDxfId="4"/>
@@ -798,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K435"/>
+  <dimension ref="A1:K437"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.375" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -15950,7 +15950,65 @@
       </c>
     </row>
     <row r="435" spans="1:10">
-      <c r="B435" s="11"/>
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435" s="1">
+        <v>46274</v>
+      </c>
+      <c r="C435" t="s">
+        <v>11</v>
+      </c>
+      <c r="D435" t="s">
+        <v>12</v>
+      </c>
+      <c r="E435" s="1">
+        <v>1</v>
+      </c>
+      <c r="F435" t="s">
+        <v>103</v>
+      </c>
+      <c r="H435" s="2">
+        <v>28320</v>
+      </c>
+      <c r="I435" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:10">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436" s="1">
+        <v>46275</v>
+      </c>
+      <c r="C436" t="s">
+        <v>11</v>
+      </c>
+      <c r="D436" t="s">
+        <v>59</v>
+      </c>
+      <c r="E436" s="1">
+        <v>1</v>
+      </c>
+      <c r="F436" t="s">
+        <v>105</v>
+      </c>
+      <c r="H436" s="2">
+        <v>8608</v>
+      </c>
+      <c r="I436" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:10">
+      <c r="B437" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/datos.xlsx
+++ b/data/datos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANGELA\Desktop\MiDashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCCAFFC-025F-4BBE-9039-37A8955EFF04}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE62F88C-5B18-472D-BC51-CB27059E5F7D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8805" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="109">
   <si>
     <t>N° DE OPERACIÓN</t>
   </si>
@@ -362,7 +362,7 @@
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -392,6 +392,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -447,7 +454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -500,11 +507,20 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -520,6 +536,10 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -613,7 +633,7 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="TIPO DE SERVICIO"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="LLENOS RECIBIDOS (EXPORTADOS)" totalsRowDxfId="3"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CONTENIDO"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Peso Neto Exportado" totalsRowDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Peso Neto Exportado" dataDxfId="5" totalsRowDxfId="2"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Peso Neto Exportado2" totalsRowDxfId="1"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="DESTINO " totalsRowDxfId="0"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Peso Neto Importado "/>
@@ -806,8 +826,8 @@
     <col min="3" max="3" width="23.125" customWidth="1"/>
     <col min="4" max="4" width="29.875" customWidth="1"/>
     <col min="5" max="5" width="31" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.625" customWidth="1"/>
-    <col min="7" max="7" width="16.75" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="24" style="1" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="19.875" style="2" customWidth="1"/>
     <col min="9" max="9" width="32" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.375" customWidth="1"/>
@@ -2993,11 +3013,11 @@
         <v>35</v>
       </c>
       <c r="G61" s="1">
-        <v>56280</v>
+        <v>56280.000000000007</v>
       </c>
       <c r="H61" s="2">
         <f t="shared" si="0"/>
-        <v>56.28</v>
+        <v>56.280000000000008</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>36</v>
@@ -3022,9 +3042,6 @@
       <c r="D62" t="s">
         <v>37</v>
       </c>
-      <c r="E62" s="1">
-        <v>0</v>
-      </c>
       <c r="F62" t="s">
         <v>35</v>
       </c>
@@ -3310,9 +3327,6 @@
       <c r="D70" t="s">
         <v>37</v>
       </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
       <c r="F70" t="s">
         <v>27</v>
       </c>
@@ -3389,11 +3403,11 @@
         <v>35</v>
       </c>
       <c r="G72" s="1">
-        <v>112560</v>
+        <v>112560.00000000001</v>
       </c>
       <c r="H72" s="2">
         <f t="shared" si="1"/>
-        <v>112.56</v>
+        <v>112.56000000000002</v>
       </c>
       <c r="I72" s="1" t="s">
         <v>36</v>
@@ -3958,9 +3972,6 @@
       <c r="D88" t="s">
         <v>37</v>
       </c>
-      <c r="E88" s="1">
-        <v>0</v>
-      </c>
       <c r="F88" t="s">
         <v>32</v>
       </c>
@@ -4462,9 +4473,6 @@
       <c r="D102" t="s">
         <v>37</v>
       </c>
-      <c r="E102" s="1">
-        <v>0</v>
-      </c>
       <c r="F102" t="s">
         <v>42</v>
       </c>
@@ -5650,9 +5658,6 @@
       <c r="D135" t="s">
         <v>37</v>
       </c>
-      <c r="E135" s="1">
-        <v>0</v>
-      </c>
       <c r="F135" t="s">
         <v>13</v>
       </c>
@@ -5686,9 +5691,6 @@
       <c r="D136" t="s">
         <v>37</v>
       </c>
-      <c r="E136" s="1">
-        <v>0</v>
-      </c>
       <c r="F136" t="s">
         <v>13</v>
       </c>
@@ -5794,9 +5796,6 @@
       <c r="D139" t="s">
         <v>37</v>
       </c>
-      <c r="E139" s="1">
-        <v>0</v>
-      </c>
       <c r="F139" t="s">
         <v>23</v>
       </c>
@@ -6262,9 +6261,6 @@
       <c r="D152" t="s">
         <v>12</v>
       </c>
-      <c r="E152" s="1">
-        <v>0</v>
-      </c>
       <c r="F152" t="s">
         <v>13</v>
       </c>
@@ -6550,9 +6546,6 @@
       <c r="D160" t="s">
         <v>37</v>
       </c>
-      <c r="E160" s="1">
-        <v>0</v>
-      </c>
       <c r="F160" t="s">
         <v>13</v>
       </c>
@@ -6622,9 +6615,6 @@
       <c r="D162" t="s">
         <v>52</v>
       </c>
-      <c r="E162" s="1">
-        <v>0</v>
-      </c>
       <c r="F162" t="s">
         <v>53</v>
       </c>
@@ -6658,9 +6648,6 @@
       <c r="D163" t="s">
         <v>52</v>
       </c>
-      <c r="E163" s="1">
-        <v>0</v>
-      </c>
       <c r="F163" t="s">
         <v>53</v>
       </c>
@@ -7810,9 +7797,6 @@
       <c r="D195" t="s">
         <v>59</v>
       </c>
-      <c r="E195" s="1">
-        <v>0</v>
-      </c>
       <c r="F195" t="s">
         <v>60</v>
       </c>
@@ -7918,9 +7902,6 @@
       <c r="D198" t="s">
         <v>59</v>
       </c>
-      <c r="E198" s="1">
-        <v>0</v>
-      </c>
       <c r="F198" t="s">
         <v>62</v>
       </c>
@@ -9358,9 +9339,6 @@
       <c r="D238" t="s">
         <v>59</v>
       </c>
-      <c r="E238" s="1">
-        <v>0</v>
-      </c>
       <c r="F238" t="s">
         <v>67</v>
       </c>
@@ -9754,9 +9732,6 @@
       <c r="D249" t="s">
         <v>52</v>
       </c>
-      <c r="E249" s="1">
-        <v>0</v>
-      </c>
       <c r="F249" t="s">
         <v>53</v>
       </c>
@@ -9790,9 +9765,6 @@
       <c r="D250" t="s">
         <v>69</v>
       </c>
-      <c r="E250" s="1">
-        <v>0</v>
-      </c>
       <c r="F250" t="s">
         <v>70</v>
       </c>
@@ -9826,9 +9798,6 @@
       <c r="D251" t="s">
         <v>69</v>
       </c>
-      <c r="E251" s="1">
-        <v>0</v>
-      </c>
       <c r="F251" t="s">
         <v>70</v>
       </c>
@@ -9862,9 +9831,6 @@
       <c r="D252" t="s">
         <v>69</v>
       </c>
-      <c r="E252" s="1">
-        <v>0</v>
-      </c>
       <c r="F252" t="s">
         <v>70</v>
       </c>
@@ -9898,9 +9864,6 @@
       <c r="D253" t="s">
         <v>69</v>
       </c>
-      <c r="E253" s="1">
-        <v>0</v>
-      </c>
       <c r="F253" t="s">
         <v>70</v>
       </c>
@@ -9934,9 +9897,6 @@
       <c r="D254" t="s">
         <v>69</v>
       </c>
-      <c r="E254" s="1">
-        <v>0</v>
-      </c>
       <c r="F254" t="s">
         <v>70</v>
       </c>
@@ -9970,9 +9930,6 @@
       <c r="D255" t="s">
         <v>69</v>
       </c>
-      <c r="E255" s="1">
-        <v>0</v>
-      </c>
       <c r="F255" t="s">
         <v>70</v>
       </c>
@@ -10006,9 +9963,6 @@
       <c r="D256" t="s">
         <v>69</v>
       </c>
-      <c r="E256" s="1">
-        <v>0</v>
-      </c>
       <c r="F256" t="s">
         <v>70</v>
       </c>
@@ -10042,9 +9996,6 @@
       <c r="D257" t="s">
         <v>69</v>
       </c>
-      <c r="E257" s="1">
-        <v>0</v>
-      </c>
       <c r="F257" t="s">
         <v>70</v>
       </c>
@@ -10078,9 +10029,6 @@
       <c r="D258" t="s">
         <v>69</v>
       </c>
-      <c r="E258" s="1">
-        <v>0</v>
-      </c>
       <c r="F258" t="s">
         <v>70</v>
       </c>
@@ -10114,9 +10062,6 @@
       <c r="D259" t="s">
         <v>52</v>
       </c>
-      <c r="E259" s="1">
-        <v>0</v>
-      </c>
       <c r="F259" t="s">
         <v>53</v>
       </c>
@@ -10150,9 +10095,6 @@
       <c r="D260" t="s">
         <v>52</v>
       </c>
-      <c r="E260" s="1">
-        <v>0</v>
-      </c>
       <c r="F260" t="s">
         <v>53</v>
       </c>
@@ -10186,9 +10128,6 @@
       <c r="D261" t="s">
         <v>52</v>
       </c>
-      <c r="E261" s="1">
-        <v>0</v>
-      </c>
       <c r="F261" t="s">
         <v>53</v>
       </c>
@@ -10258,9 +10197,6 @@
       <c r="D263" t="s">
         <v>52</v>
       </c>
-      <c r="E263" s="1">
-        <v>0</v>
-      </c>
       <c r="F263" t="s">
         <v>53</v>
       </c>
@@ -11158,9 +11094,6 @@
       <c r="D288" t="s">
         <v>69</v>
       </c>
-      <c r="E288" s="1">
-        <v>0</v>
-      </c>
       <c r="F288" t="s">
         <v>70</v>
       </c>
@@ -11194,9 +11127,6 @@
       <c r="D289" t="s">
         <v>69</v>
       </c>
-      <c r="E289" s="1">
-        <v>0</v>
-      </c>
       <c r="F289" t="s">
         <v>70</v>
       </c>
@@ -11230,9 +11160,6 @@
       <c r="D290" t="s">
         <v>69</v>
       </c>
-      <c r="E290" s="1">
-        <v>0</v>
-      </c>
       <c r="F290" t="s">
         <v>70</v>
       </c>
@@ -11266,9 +11193,6 @@
       <c r="D291" t="s">
         <v>69</v>
       </c>
-      <c r="E291" s="1">
-        <v>0</v>
-      </c>
       <c r="F291" t="s">
         <v>70</v>
       </c>
@@ -11302,9 +11226,6 @@
       <c r="D292" t="s">
         <v>69</v>
       </c>
-      <c r="E292" s="1">
-        <v>0</v>
-      </c>
       <c r="F292" t="s">
         <v>70</v>
       </c>
@@ -11338,9 +11259,6 @@
       <c r="D293" t="s">
         <v>69</v>
       </c>
-      <c r="E293" s="1">
-        <v>0</v>
-      </c>
       <c r="F293" t="s">
         <v>70</v>
       </c>
@@ -11374,9 +11292,6 @@
       <c r="D294" t="s">
         <v>69</v>
       </c>
-      <c r="E294" s="1">
-        <v>0</v>
-      </c>
       <c r="F294" t="s">
         <v>70</v>
       </c>
@@ -11410,9 +11325,6 @@
       <c r="D295" t="s">
         <v>69</v>
       </c>
-      <c r="E295" s="1">
-        <v>0</v>
-      </c>
       <c r="F295" t="s">
         <v>70</v>
       </c>
@@ -11446,9 +11358,6 @@
       <c r="D296" t="s">
         <v>69</v>
       </c>
-      <c r="E296" s="1">
-        <v>0</v>
-      </c>
       <c r="F296" t="s">
         <v>70</v>
       </c>
@@ -11590,9 +11499,6 @@
       <c r="D300" t="s">
         <v>59</v>
       </c>
-      <c r="E300" s="1">
-        <v>0</v>
-      </c>
       <c r="F300" t="s">
         <v>67</v>
       </c>
@@ -11806,9 +11712,6 @@
       <c r="D306" t="s">
         <v>12</v>
       </c>
-      <c r="E306" s="1">
-        <v>0</v>
-      </c>
       <c r="F306" t="s">
         <v>67</v>
       </c>
@@ -11914,9 +11817,6 @@
       <c r="D309" t="s">
         <v>12</v>
       </c>
-      <c r="E309" s="1">
-        <v>0</v>
-      </c>
       <c r="F309" t="s">
         <v>70</v>
       </c>
@@ -11950,9 +11850,6 @@
       <c r="D310" t="s">
         <v>69</v>
       </c>
-      <c r="E310" s="1">
-        <v>0</v>
-      </c>
       <c r="F310" t="s">
         <v>70</v>
       </c>
@@ -11986,9 +11883,6 @@
       <c r="D311" t="s">
         <v>69</v>
       </c>
-      <c r="E311" s="1">
-        <v>0</v>
-      </c>
       <c r="F311" t="s">
         <v>70</v>
       </c>
@@ -12454,9 +12348,6 @@
       <c r="D324" t="s">
         <v>80</v>
       </c>
-      <c r="E324" s="1">
-        <v>0</v>
-      </c>
       <c r="F324" t="s">
         <v>64</v>
       </c>
@@ -12850,9 +12741,6 @@
       <c r="D335" t="s">
         <v>59</v>
       </c>
-      <c r="E335" s="1">
-        <v>0</v>
-      </c>
       <c r="F335" t="s">
         <v>82</v>
       </c>
@@ -13863,7 +13751,7 @@
       <c r="F363" t="s">
         <v>76</v>
       </c>
-      <c r="G363" s="1">
+      <c r="G363" s="22">
         <v>9620</v>
       </c>
       <c r="H363" s="2">
@@ -14043,6 +13931,9 @@
       <c r="F368" t="s">
         <v>90</v>
       </c>
+      <c r="G368" s="1">
+        <v>75000</v>
+      </c>
       <c r="H368" s="2">
         <v>75</v>
       </c>
@@ -14070,10 +13961,13 @@
         <v>59</v>
       </c>
       <c r="E369" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F369" t="s">
         <v>90</v>
+      </c>
+      <c r="G369" s="1">
+        <v>50000</v>
       </c>
       <c r="H369" s="2">
         <v>75</v>
@@ -14107,6 +14001,9 @@
       <c r="F370" t="s">
         <v>91</v>
       </c>
+      <c r="G370" s="1">
+        <v>70000</v>
+      </c>
       <c r="H370" s="2">
         <v>70</v>
       </c>
@@ -14139,6 +14036,9 @@
       <c r="F371" t="s">
         <v>92</v>
       </c>
+      <c r="G371" s="1">
+        <v>70000</v>
+      </c>
       <c r="H371" s="2">
         <v>70</v>
       </c>
@@ -14171,6 +14071,9 @@
       <c r="F372" t="s">
         <v>27</v>
       </c>
+      <c r="G372" s="23">
+        <v>19380</v>
+      </c>
       <c r="H372" s="2">
         <v>19380</v>
       </c>
@@ -14203,6 +14106,9 @@
       <c r="F373" t="s">
         <v>13</v>
       </c>
+      <c r="G373" s="23">
+        <v>50000</v>
+      </c>
       <c r="H373" s="2">
         <v>50000</v>
       </c>
@@ -14235,6 +14141,9 @@
       <c r="F374" t="s">
         <v>27</v>
       </c>
+      <c r="G374" s="23">
+        <v>28420</v>
+      </c>
       <c r="H374" s="2">
         <v>28420</v>
       </c>
@@ -14267,6 +14176,9 @@
       <c r="F375" t="s">
         <v>78</v>
       </c>
+      <c r="G375" s="23">
+        <v>10665</v>
+      </c>
       <c r="H375" s="2">
         <v>10665</v>
       </c>
@@ -14276,8 +14188,8 @@
       <c r="J375">
         <v>0</v>
       </c>
-      <c r="K375" s="9">
-        <v>0</v>
+      <c r="K375" s="9" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="376" spans="1:11">
@@ -14299,6 +14211,9 @@
       <c r="F376" t="s">
         <v>95</v>
       </c>
+      <c r="G376" s="23">
+        <v>41340</v>
+      </c>
       <c r="H376" s="2">
         <v>41340</v>
       </c>
@@ -14307,6 +14222,9 @@
       </c>
       <c r="J376" s="1">
         <v>0</v>
+      </c>
+      <c r="K376" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="377" spans="1:11">
@@ -14322,14 +14240,21 @@
       <c r="D377" t="s">
         <v>59</v>
       </c>
+      <c r="E377" s="1">
+        <v>1</v>
+      </c>
       <c r="F377" t="s">
         <v>95</v>
       </c>
+      <c r="G377" s="23"/>
       <c r="I377" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J377" s="1" t="s">
         <v>96</v>
+      </c>
+      <c r="K377" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="378" spans="1:11">
@@ -14345,14 +14270,21 @@
       <c r="D378" t="s">
         <v>59</v>
       </c>
+      <c r="E378" s="1">
+        <v>3</v>
+      </c>
       <c r="F378" t="s">
         <v>95</v>
       </c>
+      <c r="G378" s="23"/>
       <c r="I378" s="1" t="s">
         <v>97</v>
       </c>
       <c r="J378" s="1">
         <v>44229</v>
+      </c>
+      <c r="K378" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="379" spans="1:11">
@@ -14368,14 +14300,21 @@
       <c r="D379" t="s">
         <v>59</v>
       </c>
+      <c r="E379" s="1">
+        <v>1</v>
+      </c>
       <c r="F379" t="s">
         <v>95</v>
       </c>
+      <c r="G379" s="23"/>
       <c r="I379" s="1" t="s">
         <v>47</v>
       </c>
       <c r="J379" s="1" t="s">
         <v>98</v>
+      </c>
+      <c r="K379" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="380" spans="1:11">
@@ -14391,18 +14330,21 @@
       <c r="D380" t="s">
         <v>59</v>
       </c>
+      <c r="E380" s="1">
+        <v>1</v>
+      </c>
       <c r="F380" t="s">
         <v>95</v>
       </c>
+      <c r="G380" s="23"/>
       <c r="I380" s="1" t="s">
         <v>34</v>
       </c>
       <c r="J380" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="K380">
-        <f>SUM(K2:K371)/1000</f>
-        <v>1494.36</v>
+      <c r="K380" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="381" spans="1:11">
@@ -14424,6 +14366,9 @@
       <c r="F381" t="s">
         <v>100</v>
       </c>
+      <c r="G381" s="23">
+        <v>8337</v>
+      </c>
       <c r="H381" s="2">
         <v>8337</v>
       </c>
@@ -14431,6 +14376,9 @@
         <v>101</v>
       </c>
       <c r="J381" s="1">
+        <v>0</v>
+      </c>
+      <c r="K381">
         <v>0</v>
       </c>
     </row>
@@ -14453,6 +14401,9 @@
       <c r="F382" t="s">
         <v>100</v>
       </c>
+      <c r="G382" s="23">
+        <v>10665</v>
+      </c>
       <c r="H382" s="2">
         <v>10665</v>
       </c>
@@ -14460,6 +14411,9 @@
         <v>24</v>
       </c>
       <c r="J382" s="1">
+        <v>0</v>
+      </c>
+      <c r="K382">
         <v>0</v>
       </c>
     </row>
@@ -14482,6 +14436,9 @@
       <c r="F383" t="s">
         <v>100</v>
       </c>
+      <c r="G383" s="23">
+        <v>100000</v>
+      </c>
       <c r="H383" s="2">
         <v>100000</v>
       </c>
@@ -14489,6 +14446,9 @@
         <v>15</v>
       </c>
       <c r="J383" s="1">
+        <v>0</v>
+      </c>
+      <c r="K383">
         <v>0</v>
       </c>
     </row>
@@ -14511,6 +14471,9 @@
       <c r="F384" t="s">
         <v>100</v>
       </c>
+      <c r="G384" s="23">
+        <v>9290</v>
+      </c>
       <c r="H384" s="2">
         <v>9290</v>
       </c>
@@ -14520,8 +14483,11 @@
       <c r="J384" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="385" spans="1:10">
+      <c r="K384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11">
       <c r="A385">
         <v>384</v>
       </c>
@@ -14540,6 +14506,9 @@
       <c r="F385" t="s">
         <v>100</v>
       </c>
+      <c r="G385" s="23">
+        <v>8560</v>
+      </c>
       <c r="H385" s="2">
         <v>8560</v>
       </c>
@@ -14549,8 +14518,11 @@
       <c r="J385" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="386" spans="1:10">
+      <c r="K385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:11">
       <c r="A386">
         <v>385</v>
       </c>
@@ -14569,6 +14541,9 @@
       <c r="F386" t="s">
         <v>100</v>
       </c>
+      <c r="G386" s="23">
+        <v>8652</v>
+      </c>
       <c r="H386" s="2">
         <v>8652</v>
       </c>
@@ -14578,8 +14553,11 @@
       <c r="J386" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="387" spans="1:10">
+      <c r="K386" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11">
       <c r="A387">
         <v>386</v>
       </c>
@@ -14598,6 +14576,9 @@
       <c r="F387" t="s">
         <v>95</v>
       </c>
+      <c r="G387" s="24">
+        <v>11520</v>
+      </c>
       <c r="H387" s="2">
         <v>11520</v>
       </c>
@@ -14607,8 +14588,11 @@
       <c r="J387" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="388" spans="1:10">
+      <c r="K387" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="388" spans="1:11">
       <c r="A388">
         <v>387</v>
       </c>
@@ -14627,6 +14611,9 @@
       <c r="F388" t="s">
         <v>100</v>
       </c>
+      <c r="G388" s="24">
+        <v>9447.5</v>
+      </c>
       <c r="H388" s="2">
         <v>9447.5</v>
       </c>
@@ -14636,8 +14623,11 @@
       <c r="J388" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="389" spans="1:10">
+      <c r="K388" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11">
       <c r="A389">
         <v>388</v>
       </c>
@@ -14656,6 +14646,9 @@
       <c r="F389" t="s">
         <v>95</v>
       </c>
+      <c r="G389" s="24">
+        <v>0</v>
+      </c>
       <c r="H389" s="2">
         <v>0</v>
       </c>
@@ -14663,10 +14656,13 @@
         <v>89</v>
       </c>
       <c r="J389" s="1">
-        <v>52995.6</v>
-      </c>
-    </row>
-    <row r="390" spans="1:10">
+        <v>52995.600000000006</v>
+      </c>
+      <c r="K389" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11">
       <c r="A390">
         <v>389</v>
       </c>
@@ -14685,6 +14681,9 @@
       <c r="F390" t="s">
         <v>95</v>
       </c>
+      <c r="G390" s="24">
+        <v>0</v>
+      </c>
       <c r="H390" s="2">
         <v>0</v>
       </c>
@@ -14692,10 +14691,13 @@
         <v>89</v>
       </c>
       <c r="J390" s="1">
-        <v>52995.6</v>
-      </c>
-    </row>
-    <row r="391" spans="1:10">
+        <v>52995.600000000006</v>
+      </c>
+      <c r="K390" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11">
       <c r="A391">
         <v>390</v>
       </c>
@@ -14714,6 +14716,9 @@
       <c r="F391" t="s">
         <v>95</v>
       </c>
+      <c r="G391" s="24">
+        <v>0</v>
+      </c>
       <c r="H391" s="2">
         <v>0</v>
       </c>
@@ -14723,8 +14728,11 @@
       <c r="J391" s="1">
         <v>4356</v>
       </c>
-    </row>
-    <row r="392" spans="1:10">
+      <c r="K391" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="392" spans="1:11">
       <c r="A392">
         <v>391</v>
       </c>
@@ -14740,6 +14748,9 @@
       <c r="F392" t="s">
         <v>100</v>
       </c>
+      <c r="G392" s="24">
+        <v>1175</v>
+      </c>
       <c r="H392" s="2">
         <v>1175</v>
       </c>
@@ -14749,8 +14760,11 @@
       <c r="J392" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="393" spans="1:10">
+      <c r="K392" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11">
       <c r="A393">
         <v>392</v>
       </c>
@@ -14769,6 +14783,9 @@
       <c r="F393" t="s">
         <v>100</v>
       </c>
+      <c r="G393" s="24">
+        <v>8500</v>
+      </c>
       <c r="H393" s="2">
         <v>8500</v>
       </c>
@@ -14776,8 +14793,11 @@
         <v>26</v>
       </c>
       <c r="J393" s="1"/>
-    </row>
-    <row r="394" spans="1:10">
+      <c r="K393" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11">
       <c r="A394">
         <v>393</v>
       </c>
@@ -14796,6 +14816,9 @@
       <c r="F394" t="s">
         <v>100</v>
       </c>
+      <c r="G394" s="24">
+        <v>9718</v>
+      </c>
       <c r="H394" s="2">
         <v>9718</v>
       </c>
@@ -14803,8 +14826,11 @@
         <v>24</v>
       </c>
       <c r="J394" s="1"/>
-    </row>
-    <row r="395" spans="1:10">
+      <c r="K394" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11">
       <c r="A395">
         <v>394</v>
       </c>
@@ -14823,6 +14849,9 @@
       <c r="F395" t="s">
         <v>100</v>
       </c>
+      <c r="G395" s="24">
+        <v>10340</v>
+      </c>
       <c r="H395" s="2">
         <v>10340</v>
       </c>
@@ -14830,8 +14859,11 @@
         <v>24</v>
       </c>
       <c r="J395" s="1"/>
-    </row>
-    <row r="396" spans="1:10">
+      <c r="K395" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11">
       <c r="A396">
         <v>395</v>
       </c>
@@ -14850,6 +14882,9 @@
       <c r="F396" t="s">
         <v>103</v>
       </c>
+      <c r="G396" s="23">
+        <v>46000</v>
+      </c>
       <c r="H396" s="2">
         <v>46000</v>
       </c>
@@ -14859,8 +14894,11 @@
       <c r="J396" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="397" spans="1:10">
+      <c r="K396" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11">
       <c r="A397">
         <v>396</v>
       </c>
@@ -14879,7 +14917,7 @@
       <c r="F397" t="s">
         <v>103</v>
       </c>
-      <c r="G397" s="1">
+      <c r="G397" s="23">
         <v>25340</v>
       </c>
       <c r="H397" s="2">
@@ -14891,8 +14929,11 @@
       <c r="J397" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="398" spans="1:10">
+      <c r="K397" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11">
       <c r="A398">
         <v>397</v>
       </c>
@@ -14908,6 +14949,9 @@
       <c r="F398" t="s">
         <v>95</v>
       </c>
+      <c r="G398" s="23">
+        <v>0</v>
+      </c>
       <c r="H398" s="2">
         <v>0</v>
       </c>
@@ -14917,8 +14961,11 @@
       <c r="J398" s="1">
         <v>2420</v>
       </c>
-    </row>
-    <row r="399" spans="1:10">
+      <c r="K398" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11">
       <c r="A399">
         <v>398</v>
       </c>
@@ -14937,7 +14984,7 @@
       <c r="F399" t="s">
         <v>105</v>
       </c>
-      <c r="G399" s="1">
+      <c r="G399" s="23">
         <v>19200</v>
       </c>
       <c r="H399" s="2">
@@ -14949,8 +14996,11 @@
       <c r="J399" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="400" spans="1:10">
+      <c r="K399" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11">
       <c r="A400">
         <v>399</v>
       </c>
@@ -14969,6 +15019,9 @@
       <c r="F400" t="s">
         <v>105</v>
       </c>
+      <c r="G400" s="23">
+        <v>10665</v>
+      </c>
       <c r="H400" s="2">
         <v>10665</v>
       </c>
@@ -14978,8 +15031,11 @@
       <c r="J400" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="401" spans="1:10">
+      <c r="K400" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11">
       <c r="A401">
         <v>400</v>
       </c>
@@ -14998,6 +15054,9 @@
       <c r="F401" t="s">
         <v>105</v>
       </c>
+      <c r="G401" s="23">
+        <v>10665</v>
+      </c>
       <c r="H401" s="2">
         <v>10665</v>
       </c>
@@ -15007,8 +15066,11 @@
       <c r="J401" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="402" spans="1:10">
+      <c r="K401" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11">
       <c r="A402">
         <v>401</v>
       </c>
@@ -15027,7 +15089,7 @@
       <c r="F402" t="s">
         <v>103</v>
       </c>
-      <c r="G402" s="1">
+      <c r="G402" s="23">
         <v>28420</v>
       </c>
       <c r="H402" s="2">
@@ -15039,8 +15101,11 @@
       <c r="J402" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="403" spans="1:10">
+      <c r="K402" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11">
       <c r="A403">
         <v>402</v>
       </c>
@@ -15059,7 +15124,7 @@
       <c r="F403" t="s">
         <v>103</v>
       </c>
-      <c r="G403" s="1">
+      <c r="G403" s="23">
         <v>28420</v>
       </c>
       <c r="H403" s="2">
@@ -15071,8 +15136,11 @@
       <c r="J403" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="404" spans="1:10">
+      <c r="K403" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11">
       <c r="A404">
         <v>403</v>
       </c>
@@ -15091,6 +15159,9 @@
       <c r="F404" t="s">
         <v>105</v>
       </c>
+      <c r="G404" s="23">
+        <v>8304</v>
+      </c>
       <c r="H404" s="2">
         <v>8304</v>
       </c>
@@ -15100,8 +15171,11 @@
       <c r="J404" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="405" spans="1:10">
+      <c r="K404" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11">
       <c r="A405">
         <v>404</v>
       </c>
@@ -15120,6 +15194,9 @@
       <c r="F405" t="s">
         <v>105</v>
       </c>
+      <c r="G405" s="1">
+        <v>3510</v>
+      </c>
       <c r="H405" s="2">
         <v>3510</v>
       </c>
@@ -15129,8 +15206,11 @@
       <c r="J405" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="406" spans="1:10">
+      <c r="K405" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11">
       <c r="A406">
         <v>405</v>
       </c>
@@ -15149,6 +15229,9 @@
       <c r="F406" t="s">
         <v>95</v>
       </c>
+      <c r="G406" s="23">
+        <v>9000</v>
+      </c>
       <c r="H406" s="2">
         <v>9000</v>
       </c>
@@ -15158,8 +15241,11 @@
       <c r="J406" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="407" spans="1:10" s="18" customFormat="1">
+      <c r="K406" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" s="18" customFormat="1">
       <c r="A407" s="18">
         <v>406</v>
       </c>
@@ -15176,7 +15262,9 @@
       <c r="F407" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G407" s="20"/>
+      <c r="G407" s="24">
+        <v>0</v>
+      </c>
       <c r="H407" s="21">
         <v>0</v>
       </c>
@@ -15186,8 +15274,11 @@
       <c r="J407" s="18">
         <v>15079.58</v>
       </c>
-    </row>
-    <row r="408" spans="1:10">
+      <c r="K407" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11">
       <c r="A408">
         <v>407</v>
       </c>
@@ -15203,6 +15294,9 @@
       <c r="F408" t="s">
         <v>95</v>
       </c>
+      <c r="G408" s="23">
+        <v>0</v>
+      </c>
       <c r="H408" s="2">
         <v>0</v>
       </c>
@@ -15212,8 +15306,11 @@
       <c r="J408">
         <v>15079.58</v>
       </c>
-    </row>
-    <row r="409" spans="1:10">
+      <c r="K408" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11">
       <c r="A409">
         <v>408</v>
       </c>
@@ -15232,6 +15329,9 @@
       <c r="F409" t="s">
         <v>95</v>
       </c>
+      <c r="G409" s="24">
+        <v>10080</v>
+      </c>
       <c r="H409" s="2">
         <v>10080</v>
       </c>
@@ -15241,8 +15341,11 @@
       <c r="J409">
         <v>0</v>
       </c>
-    </row>
-    <row r="410" spans="1:10">
+      <c r="K409" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11">
       <c r="A410">
         <v>409</v>
       </c>
@@ -15258,14 +15361,18 @@
       <c r="F410" t="s">
         <v>106</v>
       </c>
+      <c r="G410" s="23"/>
       <c r="I410" s="1" t="s">
         <v>107</v>
       </c>
       <c r="J410">
         <v>0</v>
       </c>
-    </row>
-    <row r="411" spans="1:10">
+      <c r="K410" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="411" spans="1:11">
       <c r="A411">
         <v>410</v>
       </c>
@@ -15284,6 +15391,9 @@
       <c r="F411" t="s">
         <v>105</v>
       </c>
+      <c r="G411" s="1">
+        <v>10665</v>
+      </c>
       <c r="H411" s="2">
         <v>10665</v>
       </c>
@@ -15293,8 +15403,11 @@
       <c r="J411">
         <v>0</v>
       </c>
-    </row>
-    <row r="412" spans="1:10">
+      <c r="K411" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11">
       <c r="A412">
         <v>411</v>
       </c>
@@ -15313,6 +15426,9 @@
       <c r="F412" t="s">
         <v>105</v>
       </c>
+      <c r="G412" s="1">
+        <v>3308</v>
+      </c>
       <c r="H412" s="2">
         <v>3308</v>
       </c>
@@ -15322,8 +15438,11 @@
       <c r="J412">
         <v>0</v>
       </c>
-    </row>
-    <row r="413" spans="1:10">
+      <c r="K412" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11">
       <c r="A413">
         <v>412</v>
       </c>
@@ -15342,6 +15461,9 @@
       <c r="F413" t="s">
         <v>105</v>
       </c>
+      <c r="G413" s="23">
+        <v>10665</v>
+      </c>
       <c r="H413" s="2">
         <v>10665</v>
       </c>
@@ -15351,8 +15473,11 @@
       <c r="J413">
         <v>0</v>
       </c>
-    </row>
-    <row r="414" spans="1:10">
+      <c r="K413" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11">
       <c r="A414">
         <v>413</v>
       </c>
@@ -15371,6 +15496,9 @@
       <c r="F414" t="s">
         <v>105</v>
       </c>
+      <c r="G414" s="23">
+        <v>9710.7000000000007</v>
+      </c>
       <c r="H414" s="2">
         <v>9710.7000000000007</v>
       </c>
@@ -15380,8 +15508,11 @@
       <c r="J414">
         <v>0</v>
       </c>
-    </row>
-    <row r="415" spans="1:10">
+      <c r="K414" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11">
       <c r="A415">
         <v>414</v>
       </c>
@@ -15400,6 +15531,9 @@
       <c r="F415" t="s">
         <v>105</v>
       </c>
+      <c r="G415" s="23">
+        <v>4447.1000000000004</v>
+      </c>
       <c r="H415" s="2">
         <v>4447.1000000000004</v>
       </c>
@@ -15409,8 +15543,11 @@
       <c r="J415">
         <v>0</v>
       </c>
-    </row>
-    <row r="416" spans="1:10">
+      <c r="K415" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11">
       <c r="A416">
         <v>415</v>
       </c>
@@ -15429,6 +15566,9 @@
       <c r="F416" t="s">
         <v>103</v>
       </c>
+      <c r="G416" s="23">
+        <v>24000</v>
+      </c>
       <c r="H416" s="2">
         <v>24000</v>
       </c>
@@ -15438,8 +15578,11 @@
       <c r="J416">
         <v>0</v>
       </c>
-    </row>
-    <row r="417" spans="1:10">
+      <c r="K416" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11">
       <c r="A417">
         <v>416</v>
       </c>
@@ -15458,6 +15601,9 @@
       <c r="F417" t="s">
         <v>105</v>
       </c>
+      <c r="G417" s="23">
+        <v>10063</v>
+      </c>
       <c r="H417" s="2">
         <v>10063</v>
       </c>
@@ -15467,8 +15613,11 @@
       <c r="J417">
         <v>0</v>
       </c>
-    </row>
-    <row r="418" spans="1:10">
+      <c r="K417" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11">
       <c r="A418">
         <v>417</v>
       </c>
@@ -15487,6 +15636,9 @@
       <c r="F418" t="s">
         <v>105</v>
       </c>
+      <c r="G418" s="23">
+        <v>19200</v>
+      </c>
       <c r="H418" s="2">
         <v>19200</v>
       </c>
@@ -15496,8 +15648,11 @@
       <c r="J418">
         <v>0</v>
       </c>
-    </row>
-    <row r="419" spans="1:10">
+      <c r="K418" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11">
       <c r="A419">
         <v>418</v>
       </c>
@@ -15516,6 +15671,9 @@
       <c r="F419" t="s">
         <v>103</v>
       </c>
+      <c r="G419" s="23">
+        <v>43500</v>
+      </c>
       <c r="H419" s="2">
         <v>43500</v>
       </c>
@@ -15525,8 +15683,11 @@
       <c r="J419">
         <v>0</v>
       </c>
-    </row>
-    <row r="420" spans="1:10">
+      <c r="K419" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11">
       <c r="A420">
         <v>419</v>
       </c>
@@ -15545,6 +15706,9 @@
       <c r="F420" t="s">
         <v>106</v>
       </c>
+      <c r="G420" s="23">
+        <v>24900</v>
+      </c>
       <c r="H420" s="2">
         <v>24900</v>
       </c>
@@ -15554,8 +15718,11 @@
       <c r="J420">
         <v>0</v>
       </c>
-    </row>
-    <row r="421" spans="1:10">
+      <c r="K420" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="421" spans="1:11">
       <c r="A421">
         <v>420</v>
       </c>
@@ -15571,6 +15738,9 @@
       <c r="F421" t="s">
         <v>95</v>
       </c>
+      <c r="G421" s="23">
+        <v>0</v>
+      </c>
       <c r="H421" s="2">
         <v>0</v>
       </c>
@@ -15580,8 +15750,11 @@
       <c r="J421">
         <v>15600</v>
       </c>
-    </row>
-    <row r="422" spans="1:10">
+      <c r="K421" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11">
       <c r="A422">
         <v>421</v>
       </c>
@@ -15600,6 +15773,9 @@
       <c r="F422" t="s">
         <v>105</v>
       </c>
+      <c r="G422" s="23">
+        <v>4770</v>
+      </c>
       <c r="H422" s="2">
         <v>4770</v>
       </c>
@@ -15609,8 +15785,11 @@
       <c r="J422">
         <v>0</v>
       </c>
-    </row>
-    <row r="423" spans="1:10">
+      <c r="K422" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11">
       <c r="A423">
         <v>422</v>
       </c>
@@ -15629,6 +15808,9 @@
       <c r="F423" t="s">
         <v>105</v>
       </c>
+      <c r="G423" s="23">
+        <v>8800</v>
+      </c>
       <c r="H423" s="2">
         <v>8800</v>
       </c>
@@ -15638,8 +15820,11 @@
       <c r="J423">
         <v>0</v>
       </c>
-    </row>
-    <row r="424" spans="1:10">
+      <c r="K423" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11">
       <c r="A424">
         <v>423</v>
       </c>
@@ -15658,6 +15843,9 @@
       <c r="F424" t="s">
         <v>105</v>
       </c>
+      <c r="G424" s="23">
+        <v>10433.85</v>
+      </c>
       <c r="H424" s="2">
         <v>10433.85</v>
       </c>
@@ -15667,8 +15855,11 @@
       <c r="J424">
         <v>0</v>
       </c>
-    </row>
-    <row r="425" spans="1:10">
+      <c r="K424" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11">
       <c r="A425">
         <v>424</v>
       </c>
@@ -15687,6 +15878,9 @@
       <c r="F425" t="s">
         <v>105</v>
       </c>
+      <c r="G425" s="23">
+        <v>3975.15</v>
+      </c>
       <c r="H425" s="2">
         <v>3975.15</v>
       </c>
@@ -15696,8 +15890,11 @@
       <c r="J425">
         <v>0</v>
       </c>
-    </row>
-    <row r="426" spans="1:10">
+      <c r="K425" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11">
       <c r="A426">
         <v>425</v>
       </c>
@@ -15716,6 +15913,9 @@
       <c r="F426" t="s">
         <v>103</v>
       </c>
+      <c r="G426" s="23">
+        <v>19200</v>
+      </c>
       <c r="H426" s="2">
         <v>19200</v>
       </c>
@@ -15725,8 +15925,11 @@
       <c r="J426">
         <v>0</v>
       </c>
-    </row>
-    <row r="427" spans="1:10">
+      <c r="K426" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11">
       <c r="A427">
         <v>426</v>
       </c>
@@ -15745,6 +15948,9 @@
       <c r="F427" t="s">
         <v>105</v>
       </c>
+      <c r="G427" s="23">
+        <v>55067</v>
+      </c>
       <c r="H427" s="2">
         <v>55067</v>
       </c>
@@ -15754,8 +15960,11 @@
       <c r="J427">
         <v>0</v>
       </c>
-    </row>
-    <row r="428" spans="1:10">
+      <c r="K427" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11">
       <c r="A428">
         <v>427</v>
       </c>
@@ -15774,6 +15983,9 @@
       <c r="F428" t="s">
         <v>95</v>
       </c>
+      <c r="G428" s="23">
+        <v>10360</v>
+      </c>
       <c r="H428" s="2">
         <v>10360</v>
       </c>
@@ -15783,8 +15995,11 @@
       <c r="J428">
         <v>0</v>
       </c>
-    </row>
-    <row r="429" spans="1:10">
+      <c r="K428" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="429" spans="1:11">
       <c r="A429">
         <v>428</v>
       </c>
@@ -15800,6 +16015,9 @@
       <c r="F429" t="s">
         <v>95</v>
       </c>
+      <c r="G429" s="23">
+        <v>0</v>
+      </c>
       <c r="H429" s="2">
         <v>0</v>
       </c>
@@ -15809,8 +16027,11 @@
       <c r="J429">
         <v>19005</v>
       </c>
-    </row>
-    <row r="430" spans="1:10">
+      <c r="K429" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11">
       <c r="A430">
         <v>429</v>
       </c>
@@ -15826,6 +16047,9 @@
       <c r="F430" t="s">
         <v>95</v>
       </c>
+      <c r="G430" s="23">
+        <v>0</v>
+      </c>
       <c r="H430" s="2">
         <v>0</v>
       </c>
@@ -15835,8 +16059,11 @@
       <c r="J430">
         <v>36670</v>
       </c>
-    </row>
-    <row r="431" spans="1:10">
+      <c r="K430" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11">
       <c r="A431">
         <v>430</v>
       </c>
@@ -15852,6 +16079,9 @@
       <c r="F431" t="s">
         <v>95</v>
       </c>
+      <c r="G431" s="23">
+        <v>0</v>
+      </c>
       <c r="H431" s="2">
         <v>0</v>
       </c>
@@ -15861,8 +16091,11 @@
       <c r="J431">
         <v>105990</v>
       </c>
-    </row>
-    <row r="432" spans="1:10">
+      <c r="K431" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11">
       <c r="A432">
         <v>431</v>
       </c>
@@ -15881,6 +16114,9 @@
       <c r="F432" t="s">
         <v>105</v>
       </c>
+      <c r="G432" s="23">
+        <v>4683</v>
+      </c>
       <c r="H432" s="2">
         <v>4683</v>
       </c>
@@ -15890,8 +16126,11 @@
       <c r="J432">
         <v>0</v>
       </c>
-    </row>
-    <row r="433" spans="1:10">
+      <c r="K432" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11">
       <c r="A433">
         <v>432</v>
       </c>
@@ -15910,6 +16149,9 @@
       <c r="F433" t="s">
         <v>105</v>
       </c>
+      <c r="G433" s="23">
+        <v>10525</v>
+      </c>
       <c r="H433" s="2">
         <v>10525</v>
       </c>
@@ -15919,8 +16161,11 @@
       <c r="J433">
         <v>0</v>
       </c>
-    </row>
-    <row r="434" spans="1:10">
+      <c r="K433" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11">
       <c r="A434">
         <v>433</v>
       </c>
@@ -15939,6 +16184,9 @@
       <c r="F434" t="s">
         <v>95</v>
       </c>
+      <c r="G434" s="23">
+        <v>11140</v>
+      </c>
       <c r="H434" s="2">
         <v>11140</v>
       </c>
@@ -15948,8 +16196,11 @@
       <c r="J434">
         <v>0</v>
       </c>
-    </row>
-    <row r="435" spans="1:10">
+      <c r="K434" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11">
       <c r="A435">
         <v>434</v>
       </c>
@@ -15968,6 +16219,9 @@
       <c r="F435" t="s">
         <v>103</v>
       </c>
+      <c r="G435" s="23">
+        <v>28320</v>
+      </c>
       <c r="H435" s="2">
         <v>28320</v>
       </c>
@@ -15977,8 +16231,11 @@
       <c r="J435">
         <v>0</v>
       </c>
-    </row>
-    <row r="436" spans="1:10">
+      <c r="K435" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11">
       <c r="A436">
         <v>435</v>
       </c>
@@ -15997,6 +16254,9 @@
       <c r="F436" t="s">
         <v>105</v>
       </c>
+      <c r="G436" s="23">
+        <v>8600</v>
+      </c>
       <c r="H436" s="2">
         <v>8608</v>
       </c>
@@ -16006,8 +16266,11 @@
       <c r="J436">
         <v>0</v>
       </c>
-    </row>
-    <row r="437" spans="1:10">
+      <c r="K436" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="437" spans="1:11">
       <c r="B437" s="11"/>
     </row>
   </sheetData>
